--- a/tables/Flexible CUE/Local_estpar_protection_False_vo_False_CUE_True.xlsx
+++ b/tables/Flexible CUE/Local_estpar_protection_False_vo_False_CUE_True.xlsx
@@ -573,61 +573,61 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.231221769167109</v>
+        <v>0.1686476518132877</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2007280335502076</v>
+        <v>0.1781455723476886</v>
       </c>
       <c r="M2" t="n">
-        <v>4.423003083472088</v>
+        <v>4.417326970800064</v>
       </c>
       <c r="N2" t="n">
-        <v>4.425653847148911</v>
+        <v>4.423670708055258</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001036030854336093</v>
+        <v>0.0009757843087639914</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009662860299462702</v>
+        <v>0.0008865518154754955</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007354922906390206</v>
+        <v>0.0007252836586432792</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001000328792676171</v>
+        <v>0.0009150038223330994</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006280757233780611</v>
+        <v>0.0005617456588022109</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002145773426226408</v>
+        <v>0.002054808456242891</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002469243496681151</v>
+        <v>0.002259388898014908</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001686677707755515</v>
+        <v>0.001659504395815041</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001952013490796009</v>
+        <v>0.001861137568124598</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001484384146184135</v>
+        <v>0.001389695781725496</v>
       </c>
     </row>
     <row r="3">
@@ -653,61 +653,61 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1221977047489524</v>
+        <v>0.07171408406676065</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1442518194545554</v>
+        <v>0.1017040144129667</v>
       </c>
       <c r="M3" t="n">
-        <v>4.306107642639816</v>
+        <v>4.300312826722086</v>
       </c>
       <c r="N3" t="n">
-        <v>4.337502032467726</v>
+        <v>4.330272989379029</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0007385102531921019</v>
+        <v>0.0007014693449190065</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004323092737502176</v>
+        <v>0.0003330312636565945</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0006212044380257346</v>
+        <v>0.0006164352769215213</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005406513571903711</v>
+        <v>0.0004772043276944528</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003073978134188697</v>
+        <v>0.0002646243043612541</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001528435783842365</v>
+        <v>0.001476613431214635</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001249606096496259</v>
+        <v>0.001041528434811929</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001419838742219902</v>
+        <v>0.001402928084937909</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001146019897323568</v>
+        <v>0.001064108859421947</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001092807750439923</v>
+        <v>0.001034176641797613</v>
       </c>
     </row>
     <row r="4">
@@ -733,61 +733,61 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3697996722445904</v>
+        <v>0.362659486143853</v>
       </c>
       <c r="L4" t="n">
-        <v>0.243909681991252</v>
+        <v>0.2833509849920409</v>
       </c>
       <c r="M4" t="n">
-        <v>4.407250937879116</v>
+        <v>4.40660532000618</v>
       </c>
       <c r="N4" t="n">
-        <v>4.484739514981666</v>
+        <v>4.484177291499294</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001375999236969971</v>
+        <v>0.001398238985269999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001008839880579817</v>
+        <v>0.001002016358356563</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003401607953813038</v>
+        <v>0.0003418196561957153</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001110592701613514</v>
+        <v>0.001123454909053464</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003379431905601982</v>
+        <v>0.0003618173882410734</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003010818921993113</v>
+        <v>0.003146749024230895</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002316014820505465</v>
+        <v>0.002299459725700113</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001405223071147056</v>
+        <v>0.001398668904510382</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001970513415073833</v>
+        <v>0.002123059331214608</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001897204275491919</v>
+        <v>0.001956793721674145</v>
       </c>
     </row>
     <row r="5">
@@ -813,61 +813,61 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1827280879260966</v>
+        <v>0.1240122415911155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2173228707408578</v>
+        <v>0.1729422220312712</v>
       </c>
       <c r="M5" t="n">
-        <v>4.284288814452183</v>
+        <v>4.278006377028112</v>
       </c>
       <c r="N5" t="n">
-        <v>4.352741667371737</v>
+        <v>4.344036187960216</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0009242445951582774</v>
+        <v>0.0008924123155623077</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0008760183229878889</v>
+        <v>0.0007472713051093705</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008332629381343656</v>
+        <v>0.0008113331935756313</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0008223898293157104</v>
+        <v>0.000743971846796726</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001143066033492052</v>
+        <v>0.001043177065611916</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0018846446610725</v>
+        <v>0.001855351956801206</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002341352185248148</v>
+        <v>0.002033784686702862</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001920618345477605</v>
+        <v>0.001866587167425204</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001614348006822268</v>
+        <v>0.00151032809259651</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002417924096778763</v>
+        <v>0.002243358888620908</v>
       </c>
     </row>
     <row r="6">
@@ -893,61 +893,61 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1686949453492942</v>
+        <v>0.1107046564138275</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2031628833223912</v>
+        <v>0.1512965536960488</v>
       </c>
       <c r="M6" t="n">
-        <v>4.342240366865149</v>
+        <v>4.335892868848197</v>
       </c>
       <c r="N6" t="n">
-        <v>4.389825739030086</v>
+        <v>4.383422387021119</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006513129376246789</v>
+        <v>0.0006168110399011369</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0005099148733467754</v>
+        <v>0.0003965837217878391</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005364062629132762</v>
+        <v>0.0005253635051395784</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003908347868536299</v>
+        <v>0.0003432878186302157</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003406934888335961</v>
+        <v>0.0002779362727646648</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001340626095505229</v>
+        <v>0.001292494990345785</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001277365428107233</v>
+        <v>0.00109627334027417</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001238683397870811</v>
+        <v>0.001211026171718339</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009599123526373191</v>
+        <v>0.0009056473698752273</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001003733310658616</v>
+        <v>0.0009245242847968276</v>
       </c>
     </row>
     <row r="7">
@@ -973,61 +973,61 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1697000243333415</v>
+        <v>0.1516173739293405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1652804465659608</v>
+        <v>0.1423277924039785</v>
       </c>
       <c r="M7" t="n">
-        <v>4.332467324133582</v>
+        <v>4.323072234530487</v>
       </c>
       <c r="N7" t="n">
-        <v>4.359735326752852</v>
+        <v>4.355286992566735</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009963239733623175</v>
+        <v>0.0009850174692512918</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0005862765353493547</v>
+        <v>0.0005084694717382033</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005587749000838408</v>
+        <v>0.0005486004684201943</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00089834112863101</v>
+        <v>0.0008371086384666577</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004906927437697497</v>
+        <v>0.0004477990678086707</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002081810432689104</v>
+        <v>0.002127450431704327</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001544492393458571</v>
+        <v>0.001266677630226825</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001331260007044235</v>
+        <v>0.001295807791632151</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001695463367170404</v>
+        <v>0.001641543553050302</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00190795951129067</v>
+        <v>0.001821783684497402</v>
       </c>
     </row>
     <row r="8">
@@ -1053,61 +1053,61 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1487814895648295</v>
+        <v>0.1163738173577296</v>
       </c>
       <c r="L8" t="n">
-        <v>0.164414669498079</v>
+        <v>0.1370744526426354</v>
       </c>
       <c r="M8" t="n">
-        <v>4.46691264392827</v>
+        <v>4.459073131503994</v>
       </c>
       <c r="N8" t="n">
-        <v>4.408433404547874</v>
+        <v>4.4102799167019</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001421897676553449</v>
+        <v>0.001393270363584611</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0007880902308393272</v>
+        <v>0.000706837441013797</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.001073860628852677</v>
+        <v>0.001029350956037655</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001450469299913612</v>
+        <v>0.001354700705639831</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006988789946000207</v>
+        <v>0.0006341733331961</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00318467299117844</v>
+        <v>0.003246271156957921</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002441217548879888</v>
+        <v>0.001894641318741292</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002626781525061936</v>
+        <v>0.002479156490594634</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003081919266228954</v>
+        <v>0.00300141008429361</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001530632143303958</v>
+        <v>0.001319616529204756</v>
       </c>
     </row>
     <row r="9">
@@ -1133,61 +1133,61 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1638384053732252</v>
+        <v>0.1542818023745993</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1618820064798367</v>
+        <v>0.144970064442096</v>
       </c>
       <c r="M9" t="n">
-        <v>4.269965407827312</v>
+        <v>4.264031022832119</v>
       </c>
       <c r="N9" t="n">
-        <v>4.356630140311904</v>
+        <v>4.351260184361895</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001424786628089235</v>
+        <v>0.001394929536266516</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0007677566892416287</v>
+        <v>0.0007009590226253564</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.000763834013657956</v>
+        <v>0.0007529980579755996</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0009064951698410792</v>
+        <v>0.0008519116776461808</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0008137804899998811</v>
+        <v>0.0007742505235474634</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003229348744564073</v>
+        <v>0.003271411612571289</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002077016292093021</v>
+        <v>0.00167604148595694</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001768797617125324</v>
+        <v>0.00171751411222903</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001729326432790367</v>
+        <v>0.001709254239118322</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001662266039274738</v>
+        <v>0.001579113664237122</v>
       </c>
     </row>
     <row r="10">
@@ -1213,61 +1213,61 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2045760244746017</v>
+        <v>0.1626744216582501</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1178975603887778</v>
+        <v>0.1115454482106549</v>
       </c>
       <c r="M10" t="n">
-        <v>4.174498702949626</v>
+        <v>4.162069417286844</v>
       </c>
       <c r="N10" t="n">
-        <v>4.218725834950201</v>
+        <v>4.209610456872686</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001250047381532973</v>
+        <v>0.001235717519786987</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0006661671678923572</v>
+        <v>0.0006323168769020998</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0005633092942195461</v>
+        <v>0.0005520972200354908</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001056221765138765</v>
+        <v>0.000948610896789548</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005963732500469715</v>
+        <v>0.0005690230938987514</v>
       </c>
       <c r="T10" t="n">
-        <v>0.002821938578356566</v>
+        <v>0.002870530231901877</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001508728437104623</v>
+        <v>0.001441196247476929</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001324399112507671</v>
+        <v>0.001297198501377103</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001976055606821254</v>
+        <v>0.0018446133251703</v>
       </c>
       <c r="X10" t="n">
-        <v>0.001314642337750364</v>
+        <v>0.001304240194329366</v>
       </c>
     </row>
     <row r="11">
@@ -1293,61 +1293,61 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1492016749720489</v>
+        <v>0.1501508153581676</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3054793298909592</v>
+        <v>0.3103323140627094</v>
       </c>
       <c r="M11" t="n">
-        <v>4.076850431013222</v>
+        <v>4.073295245127875</v>
       </c>
       <c r="N11" t="n">
-        <v>4.249960457418712</v>
+        <v>4.250322034257744</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002094941687139731</v>
+        <v>0.002170537247299432</v>
       </c>
       <c r="P11" t="n">
-        <v>0.00107245292044318</v>
+        <v>0.001106200251273516</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.001174881363618315</v>
+        <v>0.001117594335954647</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001652288951391396</v>
+        <v>0.001646994907991974</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001547213472431677</v>
+        <v>0.00154315550019146</v>
       </c>
       <c r="T11" t="n">
-        <v>0.005242279763037251</v>
+        <v>0.005506190299502879</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003430893704976162</v>
+        <v>0.003766313064512017</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003060050642526334</v>
+        <v>0.002887134471991618</v>
       </c>
       <c r="W11" t="n">
-        <v>0.004568109271056386</v>
+        <v>0.004916105639512667</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003694809392214986</v>
+        <v>0.003792519148302907</v>
       </c>
     </row>
     <row r="12">
@@ -1373,61 +1373,61 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09975764557508193</v>
+        <v>0.08303556085308046</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1659138125870586</v>
+        <v>0.1270378462503029</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05812402486322</v>
+        <v>4.064957109306907</v>
       </c>
       <c r="N12" t="n">
-        <v>4.121198414110867</v>
+        <v>4.106414873100161</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0004070062647672804</v>
+        <v>0.0004580417836006846</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0006391306610541545</v>
+        <v>0.000355685464985223</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0004710583345942271</v>
+        <v>0.0004975061094990432</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001568313178404216</v>
+        <v>0.001236902840326772</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0005164320981140263</v>
+        <v>0.0004789084689367212</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0009992219690301563</v>
+        <v>0.001081470076239653</v>
       </c>
       <c r="U12" t="n">
-        <v>0.003280344694183409</v>
+        <v>0.003572165389498966</v>
       </c>
       <c r="V12" t="n">
-        <v>0.00109592359202617</v>
+        <v>0.001157591141985895</v>
       </c>
       <c r="W12" t="n">
-        <v>0.006830875014362864</v>
+        <v>0.00805719896369762</v>
       </c>
       <c r="X12" t="n">
-        <v>0.001093449290929939</v>
+        <v>0.001086124295563002</v>
       </c>
     </row>
     <row r="13">
@@ -1453,61 +1453,61 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1219723482576723</v>
+        <v>0.1046052363559759</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2094789931670664</v>
+        <v>0.1784491804221781</v>
       </c>
       <c r="M13" t="n">
-        <v>4.289380695969489</v>
+        <v>4.284498936397276</v>
       </c>
       <c r="N13" t="n">
-        <v>4.510143170895798</v>
+        <v>4.513139272845926</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0009988403582332054</v>
+        <v>0.0009421068974899029</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0007499320993549638</v>
+        <v>0.0005682635139466571</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0009121457561691423</v>
+        <v>0.000870989140611081</v>
       </c>
       <c r="R13" t="n">
-        <v>0.008568734635633422</v>
+        <v>0.008374017835491252</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01469303671493151</v>
+        <v>0.01450074015935809</v>
       </c>
       <c r="T13" t="n">
-        <v>0.007580942476904368</v>
+        <v>0.007281388864759957</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01981972397282626</v>
+        <v>0.01851396958731733</v>
       </c>
       <c r="V13" t="n">
-        <v>0.00713045918068616</v>
+        <v>0.006942902247740058</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02260045542251728</v>
+        <v>0.02166673462803347</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03912104995057115</v>
+        <v>0.03824997106554937</v>
       </c>
     </row>
     <row r="14">
@@ -1533,61 +1533,61 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1913164990551056</v>
+        <v>0.1423061650191516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2978122170830621</v>
+        <v>0.2373555557239639</v>
       </c>
       <c r="M14" t="n">
-        <v>4.361494374090167</v>
+        <v>4.34857888340721</v>
       </c>
       <c r="N14" t="n">
-        <v>4.37321107077672</v>
+        <v>4.365107485282588</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00599232816544145</v>
+        <v>0.005874642265403582</v>
       </c>
       <c r="P14" t="n">
-        <v>0.001700886879112241</v>
+        <v>0.0006655851969653212</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.008418503671921741</v>
+        <v>0.007952202294511785</v>
       </c>
       <c r="R14" t="n">
-        <v>0.007051973554018902</v>
+        <v>0.006066188142494658</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01089557024575488</v>
+        <v>0.008830877531371845</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01156278605021886</v>
+        <v>0.01153001023279127</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0118526805864358</v>
+        <v>0.009219643948573421</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01763089842710312</v>
+        <v>0.01658450685047231</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01476641824446299</v>
+        <v>0.01342703200450457</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02972763512842828</v>
+        <v>0.02600593656074506</v>
       </c>
     </row>
     <row r="15">
@@ -1613,61 +1613,61 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.18717447583358</v>
+        <v>0.1304836268708661</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2802752231301741</v>
+        <v>0.2250345735371539</v>
       </c>
       <c r="M15" t="n">
-        <v>4.078910665279218</v>
+        <v>4.071216775025594</v>
       </c>
       <c r="N15" t="n">
-        <v>4.255520849975503</v>
+        <v>4.236733696179028</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00607586072160539</v>
+        <v>0.005833434179653676</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002444229941098794</v>
+        <v>0.001718759962112743</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.008014431497273503</v>
+        <v>0.007793192043241314</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005477766760053277</v>
+        <v>0.00452527309090206</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02492501218807375</v>
+        <v>0.02251332072834291</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01187881636543209</v>
+        <v>0.01153415500789025</v>
       </c>
       <c r="U15" t="n">
-        <v>0.008338162958266455</v>
+        <v>0.00767555979538294</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01709898557325353</v>
+        <v>0.01662350054001277</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01170941390785224</v>
+        <v>0.01075584225253598</v>
       </c>
       <c r="X15" t="n">
-        <v>0.08581813255588283</v>
+        <v>0.07552333260644956</v>
       </c>
     </row>
     <row r="16">
@@ -1693,61 +1693,61 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5236690839066376</v>
+        <v>0.5116905935028913</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5447768992630679</v>
+        <v>0.5582179888756231</v>
       </c>
       <c r="M16" t="n">
-        <v>4.405739545165345</v>
+        <v>4.397292039063695</v>
       </c>
       <c r="N16" t="n">
-        <v>4.588775395438945</v>
+        <v>4.544704064845276</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02629433258354745</v>
+        <v>0.02710443282381944</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01825767335536112</v>
+        <v>0.01899889833695825</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01995705346006832</v>
+        <v>0.02074691719071987</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01271085112942659</v>
+        <v>0.01319821921476901</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001687308682514193</v>
+        <v>0.005372192387672814</v>
       </c>
       <c r="T16" t="n">
-        <v>0.07843503510841023</v>
+        <v>0.2239777452380434</v>
       </c>
       <c r="U16" t="n">
-        <v>0.04261755193331022</v>
+        <v>0.1979543662694198</v>
       </c>
       <c r="V16" t="n">
-        <v>0.05173303355811669</v>
+        <v>0.2233512148783388</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02890125780247119</v>
+        <v>0.1297776657704041</v>
       </c>
       <c r="X16" t="n">
-        <v>11.82870769866166</v>
+        <v>25.43621666171475</v>
       </c>
     </row>
     <row r="17">
@@ -1773,61 +1773,61 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1754337283424276</v>
+        <v>0.1561989488837014</v>
       </c>
       <c r="L17" t="n">
-        <v>0.258181785565896</v>
+        <v>0.2088196181295663</v>
       </c>
       <c r="M17" t="n">
-        <v>3.87520233994104</v>
+        <v>3.852813853820157</v>
       </c>
       <c r="N17" t="n">
-        <v>4.032244118696998</v>
+        <v>4.001696627628808</v>
       </c>
       <c r="O17" t="n">
-        <v>0.006628588980838948</v>
+        <v>0.006334073447950004</v>
       </c>
       <c r="P17" t="n">
-        <v>0.001420039364258143</v>
+        <v>0.000906638687091994</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.006632446521555598</v>
+        <v>0.006530328641540274</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004413668318690122</v>
+        <v>0.003586959468513591</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01062507074458074</v>
+        <v>0.0102591741582876</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01251939859350267</v>
+        <v>0.01227441703230978</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01112140058037017</v>
+        <v>0.007736076548526278</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01390929461282206</v>
+        <v>0.01365508400205086</v>
       </c>
       <c r="W17" t="n">
-        <v>0.01076699410921815</v>
+        <v>0.009265959544246286</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02079357850819201</v>
+        <v>0.02019431468527703</v>
       </c>
     </row>
     <row r="18">
@@ -1853,61 +1853,61 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2418615173003435</v>
+        <v>0.1810731846415948</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2681515006642515</v>
+        <v>0.2181092683628255</v>
       </c>
       <c r="M18" t="n">
-        <v>4.288454172770764</v>
+        <v>4.276187403986832</v>
       </c>
       <c r="N18" t="n">
-        <v>4.303917415553972</v>
+        <v>4.291835403197044</v>
       </c>
       <c r="O18" t="n">
-        <v>0.006354930986453526</v>
+        <v>0.006119988688782077</v>
       </c>
       <c r="P18" t="n">
-        <v>0.003316946237538857</v>
+        <v>0.002702866377362795</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.00617889385079171</v>
+        <v>0.005999154585284629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008460450925388378</v>
+        <v>0.007473200511921923</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008839901297548964</v>
+        <v>0.008090665312753785</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01222665699264168</v>
+        <v>0.0119448121924151</v>
       </c>
       <c r="U18" t="n">
-        <v>0.007879625900262787</v>
+        <v>0.007412375456742773</v>
       </c>
       <c r="V18" t="n">
-        <v>0.01296826132184478</v>
+        <v>0.01265969514333957</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0145969988759406</v>
+        <v>0.01366251991852288</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01528863024555051</v>
+        <v>0.01448441209002495</v>
       </c>
     </row>
     <row r="19">
@@ -1933,61 +1933,61 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1612348717429317</v>
+        <v>0.1079340709237017</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2284373787715951</v>
+        <v>0.1727510320306107</v>
       </c>
       <c r="M19" t="n">
-        <v>3.995533644292064</v>
+        <v>4.005920821418274</v>
       </c>
       <c r="N19" t="n">
-        <v>4.385763809875796</v>
+        <v>4.379023530119922</v>
       </c>
       <c r="O19" t="n">
-        <v>0.00194459338997969</v>
+        <v>0.001814940835121918</v>
       </c>
       <c r="P19" t="n">
-        <v>0.003959370231902597</v>
+        <v>0.003190989711038909</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003597070675520183</v>
+        <v>0.003556595312604569</v>
       </c>
       <c r="R19" t="n">
-        <v>0.001510380119632769</v>
+        <v>0.001349804416226465</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03201946511225367</v>
+        <v>0.02896522921583519</v>
       </c>
       <c r="T19" t="n">
-        <v>0.007007661678757926</v>
+        <v>0.006829559742851742</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01015180550138561</v>
+        <v>0.009022359902684067</v>
       </c>
       <c r="V19" t="n">
-        <v>0.009274064412685577</v>
+        <v>0.009171924749399691</v>
       </c>
       <c r="W19" t="n">
-        <v>0.006864381470667107</v>
+        <v>0.006570345463227629</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1629009453554489</v>
+        <v>0.1366204167017181</v>
       </c>
     </row>
     <row r="20">
@@ -2013,61 +2013,61 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2693988039088081</v>
+        <v>0.2045934972566862</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2994937298866724</v>
+        <v>0.2445265251248257</v>
       </c>
       <c r="M20" t="n">
-        <v>4.607232881973829</v>
+        <v>4.607241387038218</v>
       </c>
       <c r="N20" t="n">
-        <v>4.593855003128358</v>
+        <v>4.59879498485235</v>
       </c>
       <c r="O20" t="n">
-        <v>0.004119698273969235</v>
+        <v>0.003919247495021191</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0004660370212787745</v>
+        <v>1.000000000000011e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.004591309189927666</v>
+        <v>0.004578083742521547</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005455640808046824</v>
+        <v>0.005038553389808509</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01534886885829504</v>
+        <v>0.01269100395002215</v>
       </c>
       <c r="T20" t="n">
-        <v>0.009213643772673278</v>
+        <v>0.008971002112388922</v>
       </c>
       <c r="U20" t="n">
-        <v>0.00821668555849343</v>
+        <v>0.007935543414147619</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01045735940839868</v>
+        <v>0.01039915313514054</v>
       </c>
       <c r="W20" t="n">
-        <v>0.01137763685064642</v>
+        <v>0.01086195564525674</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02904363820603907</v>
+        <v>0.02581650345265067</v>
       </c>
     </row>
     <row r="21">
@@ -2093,61 +2093,61 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.120044065289244</v>
+        <v>0.07219559147808233</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1352945028194716</v>
+        <v>0.1375807674251951</v>
       </c>
       <c r="M21" t="n">
-        <v>4.099687029519429</v>
+        <v>4.140908318302595</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1248923715668</v>
+        <v>4.145910995847281</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00407662249469456</v>
+        <v>0.003769891924708079</v>
       </c>
       <c r="P21" t="n">
-        <v>0.01295613900107324</v>
+        <v>0.0124024005593451</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.004952782037304549</v>
+        <v>0.007379913157689356</v>
       </c>
       <c r="R21" t="n">
-        <v>1.000000000027827e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="S21" t="n">
-        <v>1.000000000000022e-05</v>
+        <v>1.000000000000014e-05</v>
       </c>
       <c r="T21" t="n">
-        <v>0.009137433873018961</v>
+        <v>0.008852571195289385</v>
       </c>
       <c r="U21" t="n">
-        <v>0.02788412243765577</v>
+        <v>0.0265382321631869</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01435673770158626</v>
+        <v>0.02434217064629895</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01092755132246841</v>
+        <v>0.01269297330453158</v>
       </c>
       <c r="X21" t="n">
-        <v>0.03374527209909096</v>
+        <v>0.05693601364072064</v>
       </c>
     </row>
     <row r="22">
@@ -2173,61 +2173,61 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2811593684201072</v>
+        <v>0.2535001507163447</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3219336897784825</v>
+        <v>0.2746468174846994</v>
       </c>
       <c r="M22" t="n">
-        <v>4.136621870834812</v>
+        <v>4.128946614370499</v>
       </c>
       <c r="N22" t="n">
-        <v>4.310555080316768</v>
+        <v>4.298116970700001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.003452519475423095</v>
+        <v>0.003361516846492695</v>
       </c>
       <c r="P22" t="n">
-        <v>1.000000000293891e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002667760882931831</v>
+        <v>0.002651885585703412</v>
       </c>
       <c r="R22" t="n">
-        <v>0.003427522285985653</v>
+        <v>0.003186148105360714</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01261766381550549</v>
+        <v>0.01200381895283259</v>
       </c>
       <c r="T22" t="n">
-        <v>0.008737663070298317</v>
+        <v>0.008602907932364045</v>
       </c>
       <c r="U22" t="n">
-        <v>0.008893291104462978</v>
+        <v>0.006614021433434959</v>
       </c>
       <c r="V22" t="n">
-        <v>0.008472705799413272</v>
+        <v>0.008396758203211089</v>
       </c>
       <c r="W22" t="n">
-        <v>0.009323941641885125</v>
+        <v>0.008701089856572706</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02761844603714808</v>
+        <v>0.0260338333428642</v>
       </c>
     </row>
     <row r="23">
@@ -2253,61 +2253,61 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2096861360727826</v>
+        <v>0.1847131896747425</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2756548665652951</v>
+        <v>0.2351618068355882</v>
       </c>
       <c r="M23" t="n">
-        <v>3.857921490702031</v>
+        <v>3.850086826112817</v>
       </c>
       <c r="N23" t="n">
-        <v>4.108324366475617</v>
+        <v>4.086492549256411</v>
       </c>
       <c r="O23" t="n">
-        <v>0.005893923458297847</v>
+        <v>0.005774482525932781</v>
       </c>
       <c r="P23" t="n">
-        <v>0.00239599920831833</v>
+        <v>0.001925672317890849</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.004057091880611968</v>
+        <v>0.003928288460270477</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006249384655971784</v>
+        <v>0.005107378995402776</v>
       </c>
       <c r="S23" t="n">
-        <v>0.02459890770696223</v>
+        <v>0.02293230519342301</v>
       </c>
       <c r="T23" t="n">
-        <v>0.01161944645866636</v>
+        <v>0.01147385682567555</v>
       </c>
       <c r="U23" t="n">
-        <v>0.01123877098909928</v>
+        <v>0.01019550079513259</v>
       </c>
       <c r="V23" t="n">
-        <v>0.00988566345542425</v>
+        <v>0.009700898933208293</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0160228893478535</v>
+        <v>0.01425516662537029</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0779479599141152</v>
+        <v>0.07031827121414996</v>
       </c>
     </row>
     <row r="24">
@@ -2333,61 +2333,61 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3822690760043342</v>
+        <v>0.3277679418815057</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4470791483950528</v>
+        <v>0.4277291089190278</v>
       </c>
       <c r="M24" t="n">
-        <v>4.250849247723202</v>
+        <v>4.117347210101763</v>
       </c>
       <c r="N24" t="n">
-        <v>4.315631253518427</v>
+        <v>4.262493017713639</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01081685253349735</v>
+        <v>0.01068398898360446</v>
       </c>
       <c r="P24" t="n">
-        <v>0.007703572560213488</v>
+        <v>0.007388141622463791</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0130255083043113</v>
+        <v>0.01275328886727705</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01294350498449111</v>
+        <v>0.01219095645453148</v>
       </c>
       <c r="S24" t="n">
-        <v>0.00512140937954691</v>
+        <v>0.03086638826663004</v>
       </c>
       <c r="T24" t="n">
-        <v>0.02313969012479855</v>
+        <v>0.034668415230471</v>
       </c>
       <c r="U24" t="n">
-        <v>0.01877459816268068</v>
+        <v>0.04316947575877116</v>
       </c>
       <c r="V24" t="n">
-        <v>0.03249401946134126</v>
+        <v>0.04811117458730145</v>
       </c>
       <c r="W24" t="n">
-        <v>0.04108209593454463</v>
+        <v>0.1148754219931374</v>
       </c>
       <c r="X24" t="n">
-        <v>5.667988297074819</v>
+        <v>140.2728113701399</v>
       </c>
     </row>
     <row r="25">
@@ -2413,61 +2413,61 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2154668003430986</v>
+        <v>0.1551151330948538</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2293733885558452</v>
+        <v>0.1744404709257418</v>
       </c>
       <c r="M25" t="n">
-        <v>4.303014593509248</v>
+        <v>4.304155391582155</v>
       </c>
       <c r="N25" t="n">
-        <v>4.342454821898649</v>
+        <v>4.342588445229381</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0009243203275295116</v>
+        <v>0.000914277827500179</v>
       </c>
       <c r="P25" t="n">
         <v>1e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0005530269389838073</v>
+        <v>0.0006132294782528755</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0003331330087139958</v>
+        <v>0.0003116606984446847</v>
       </c>
       <c r="S25" t="n">
-        <v>9.783676293404874e-05</v>
+        <v>6.970117959606651e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>0.001858507017031442</v>
+        <v>0.001842887793927331</v>
       </c>
       <c r="U25" t="n">
-        <v>0.00119593230768774</v>
+        <v>0.001176768147386531</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001547969601215409</v>
+        <v>0.001615804060575276</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001346818174773276</v>
+        <v>0.001307842896869543</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001313410323274615</v>
+        <v>0.001296395903823144</v>
       </c>
     </row>
     <row r="26">
@@ -2493,61 +2493,61 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3206536186429215</v>
+        <v>0.2666797233848718</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3143408561555466</v>
+        <v>0.2627751303327483</v>
       </c>
       <c r="M26" t="n">
-        <v>4.234787854458681</v>
+        <v>4.221753200887219</v>
       </c>
       <c r="N26" t="n">
-        <v>4.297161793057659</v>
+        <v>4.284272935395412</v>
       </c>
       <c r="O26" t="n">
-        <v>0.001613431803254446</v>
+        <v>0.00158210519702784</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0008943014091062341</v>
+        <v>0.0007094678685056231</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0007081676253361222</v>
+        <v>0.0006754236345093261</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005575397425509987</v>
+        <v>0.0004847356892278518</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0003246583029629219</v>
+        <v>0.0002734652633379807</v>
       </c>
       <c r="T26" t="n">
-        <v>0.002680469741764062</v>
+        <v>0.002653873419817038</v>
       </c>
       <c r="U26" t="n">
-        <v>0.001464910474576186</v>
+        <v>0.001333102519337465</v>
       </c>
       <c r="V26" t="n">
-        <v>0.001763129529915675</v>
+        <v>0.00172737067153049</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001519796793220804</v>
+        <v>0.001450409909589445</v>
       </c>
       <c r="X26" t="n">
-        <v>0.001261535720323833</v>
+        <v>0.001235845370002145</v>
       </c>
     </row>
     <row r="27">
@@ -2573,61 +2573,61 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2430405588533768</v>
+        <v>0.1844609830677478</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3052212311756684</v>
+        <v>0.2508495573201208</v>
       </c>
       <c r="M27" t="n">
-        <v>4.135167174011909</v>
+        <v>4.115975320209331</v>
       </c>
       <c r="N27" t="n">
-        <v>4.152361558197282</v>
+        <v>4.127756835856357</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0008362570910478658</v>
+        <v>0.0008067437199978897</v>
       </c>
       <c r="P27" t="n">
-        <v>0.00032418005317086</v>
+        <v>0.0001434081635684251</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001195827500999862</v>
+        <v>0.001173212466148055</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0006320535875846396</v>
+        <v>0.0005171130362826565</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0007174695644330698</v>
+        <v>0.0006761806354228812</v>
       </c>
       <c r="T27" t="n">
-        <v>0.001678440569950307</v>
+        <v>0.001637482319988059</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0014695133274421</v>
+        <v>0.001319547563701633</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002443476010021269</v>
+        <v>0.002410411293333479</v>
       </c>
       <c r="W27" t="n">
-        <v>0.001683589948405361</v>
+        <v>0.001574598892946563</v>
       </c>
       <c r="X27" t="n">
-        <v>0.001788220108048311</v>
+        <v>0.001760089473779786</v>
       </c>
     </row>
     <row r="28">
@@ -2653,61 +2653,61 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3989682187359773</v>
+        <v>0.3641271367988411</v>
       </c>
       <c r="L28" t="n">
-        <v>0.4092629046958196</v>
+        <v>0.3958030021543615</v>
       </c>
       <c r="M28" t="n">
-        <v>4.115059320054375</v>
+        <v>4.118047418263454</v>
       </c>
       <c r="N28" t="n">
-        <v>4.293078471558147</v>
+        <v>4.287790874843105</v>
       </c>
       <c r="O28" t="n">
-        <v>0.001534024895072808</v>
+        <v>0.001538320979658801</v>
       </c>
       <c r="P28" t="n">
-        <v>1.000000000000011e-05</v>
+        <v>1.000000000001195e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.001498308086895604</v>
+        <v>0.001522223933141005</v>
       </c>
       <c r="R28" t="n">
-        <v>0.005015469150943665</v>
+        <v>0.004951721398483424</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0103671300368231</v>
+        <v>0.0101350479235296</v>
       </c>
       <c r="T28" t="n">
-        <v>0.003159239991356353</v>
+        <v>0.003181832835056997</v>
       </c>
       <c r="U28" t="n">
-        <v>0.00825586349003072</v>
+        <v>0.009205434022545053</v>
       </c>
       <c r="V28" t="n">
-        <v>0.003291355110636551</v>
+        <v>0.003393796783452199</v>
       </c>
       <c r="W28" t="n">
-        <v>0.009613436860977745</v>
+        <v>0.01025758035277852</v>
       </c>
       <c r="X28" t="n">
-        <v>0.02351806728635009</v>
+        <v>0.02317867063742814</v>
       </c>
     </row>
     <row r="29">
@@ -2733,61 +2733,61 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5374259014890495</v>
+        <v>0.5420877920164093</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3604601450582132</v>
+        <v>0.522889305453539</v>
       </c>
       <c r="M29" t="n">
-        <v>4.282902876970244</v>
+        <v>4.322202820865563</v>
       </c>
       <c r="N29" t="n">
-        <v>4.20670847511995</v>
+        <v>4.268109440207473</v>
       </c>
       <c r="O29" t="n">
-        <v>0.003373715698412262</v>
+        <v>0.003878766615762633</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01785487757802002</v>
+        <v>0.01888218552677088</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0002407743994858941</v>
+        <v>0.0008627578622603392</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01724638504779197</v>
+        <v>0.02115239374430709</v>
       </c>
       <c r="S29" t="n">
-        <v>0.009325626751094608</v>
+        <v>0.01036194886198784</v>
       </c>
       <c r="T29" t="n">
-        <v>0.005132768649515351</v>
+        <v>0.006267378196754303</v>
       </c>
       <c r="U29" t="n">
-        <v>0.07060036645165979</v>
+        <v>0.07505802953975263</v>
       </c>
       <c r="V29" t="n">
-        <v>0.003207955663695086</v>
+        <v>0.003560736423595471</v>
       </c>
       <c r="W29" t="n">
-        <v>0.03459126219839078</v>
+        <v>0.04824849425643082</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01594575176843815</v>
+        <v>0.01785782803572563</v>
       </c>
     </row>
     <row r="30">
@@ -2813,61 +2813,61 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4720730841162494</v>
+        <v>0.4777226216200164</v>
       </c>
       <c r="L30" t="n">
-        <v>0.4060255369959981</v>
+        <v>0.4497425184979219</v>
       </c>
       <c r="M30" t="n">
-        <v>4.562326845844513</v>
+        <v>4.562125443659149</v>
       </c>
       <c r="N30" t="n">
-        <v>4.310992643482799</v>
+        <v>4.318495095740625</v>
       </c>
       <c r="O30" t="n">
-        <v>0.001928383891359916</v>
+        <v>0.002029144812969843</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004068914948481573</v>
+        <v>0.004367359681368378</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0002226821519782366</v>
+        <v>0.000304754601094176</v>
       </c>
       <c r="R30" t="n">
-        <v>0.009076009951212084</v>
+        <v>0.009634248111694802</v>
       </c>
       <c r="S30" t="n">
-        <v>0.004120885340257131</v>
+        <v>0.004442766642216734</v>
       </c>
       <c r="T30" t="n">
-        <v>0.003298519468737338</v>
+        <v>0.003525021579236128</v>
       </c>
       <c r="U30" t="n">
-        <v>0.007509762989174581</v>
+        <v>0.008246584026229794</v>
       </c>
       <c r="V30" t="n">
-        <v>0.003110581273658145</v>
+        <v>0.003257713547189084</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01497550629745785</v>
+        <v>0.01673494134043381</v>
       </c>
       <c r="X30" t="n">
-        <v>0.005719795584832593</v>
+        <v>0.006234228556000868</v>
       </c>
     </row>
     <row r="31">
@@ -2893,61 +2893,61 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4939662194456111</v>
+        <v>0.4787482540209079</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4304051842043197</v>
+        <v>0.4351165754737921</v>
       </c>
       <c r="M31" t="n">
-        <v>4.280086717342922</v>
+        <v>4.278628979684508</v>
       </c>
       <c r="N31" t="n">
-        <v>4.392091923124475</v>
+        <v>4.390877193702263</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002212569642459092</v>
+        <v>0.002201474452063921</v>
       </c>
       <c r="P31" t="n">
-        <v>0.005756204075930939</v>
+        <v>0.005753689933667507</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0002681450838371158</v>
+        <v>0.0002574077180274379</v>
       </c>
       <c r="R31" t="n">
-        <v>0.001796872263137101</v>
+        <v>0.001778407350455104</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0005729792831041041</v>
+        <v>0.00055974572474833</v>
       </c>
       <c r="T31" t="n">
-        <v>0.003720448129265789</v>
+        <v>0.003740356175967931</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01265458249049705</v>
+        <v>0.01302328158800875</v>
       </c>
       <c r="V31" t="n">
-        <v>0.002572472276813907</v>
+        <v>0.002621383751430529</v>
       </c>
       <c r="W31" t="n">
-        <v>0.003043422605614916</v>
+        <v>0.003153010239280609</v>
       </c>
       <c r="X31" t="n">
-        <v>0.002831167689119767</v>
+        <v>0.002893850745856871</v>
       </c>
     </row>
     <row r="32">
@@ -2973,61 +2973,61 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5041910255103661</v>
+        <v>0.4809602673783849</v>
       </c>
       <c r="L32" t="n">
-        <v>0.427252988656721</v>
+        <v>0.4335280661008496</v>
       </c>
       <c r="M32" t="n">
-        <v>4.563241224115946</v>
+        <v>4.566585713233426</v>
       </c>
       <c r="N32" t="n">
-        <v>4.417612467237852</v>
+        <v>4.415995232459434</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0006691893135036334</v>
+        <v>0.0006847788751482901</v>
       </c>
       <c r="P32" t="n">
-        <v>0.00405671385392055</v>
+        <v>0.004157373419996939</v>
       </c>
       <c r="Q32" t="n">
         <v>1e-05</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004431448153823202</v>
+        <v>0.004560549769790144</v>
       </c>
       <c r="S32" t="n">
-        <v>0.001410318523168742</v>
+        <v>0.001422755174828777</v>
       </c>
       <c r="T32" t="n">
-        <v>0.002112257329904021</v>
+        <v>0.002137869252250389</v>
       </c>
       <c r="U32" t="n">
-        <v>0.008645398930070245</v>
+        <v>0.00906382775149874</v>
       </c>
       <c r="V32" t="n">
-        <v>0.00260731026014895</v>
+        <v>0.002630002707977629</v>
       </c>
       <c r="W32" t="n">
-        <v>0.00813856008353521</v>
+        <v>0.008753552894219764</v>
       </c>
       <c r="X32" t="n">
-        <v>0.003607290030651333</v>
+        <v>0.003659202178161485</v>
       </c>
     </row>
     <row r="33">
@@ -3051,61 +3051,61 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2828125477845588</v>
+        <v>0.2241840487608926</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2943164256458368</v>
+        <v>0.2571359088954341</v>
       </c>
       <c r="M33" t="n">
-        <v>4.275571175206728</v>
+        <v>4.264159583875831</v>
       </c>
       <c r="N33" t="n">
-        <v>4.266011128939271</v>
+        <v>4.255131042121516</v>
       </c>
       <c r="O33" t="n">
-        <v>0.003721062055523678</v>
+        <v>0.003568178526699263</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002004240594218346</v>
+        <v>0.001369238678037555</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.003536156447389961</v>
+        <v>0.003487948926234275</v>
       </c>
       <c r="R33" t="n">
-        <v>0.007089830074720422</v>
+        <v>0.006267396568362716</v>
       </c>
       <c r="S33" t="n">
-        <v>0.003920018428343979</v>
+        <v>0.003504997178617085</v>
       </c>
       <c r="T33" t="n">
-        <v>0.00707167874812322</v>
+        <v>0.006824545208163823</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01473158019449354</v>
+        <v>0.01694966701772099</v>
       </c>
       <c r="V33" t="n">
-        <v>0.007670801010774816</v>
+        <v>0.007667227435563432</v>
       </c>
       <c r="W33" t="n">
-        <v>0.01264043800390412</v>
+        <v>0.01247886591581</v>
       </c>
       <c r="X33" t="n">
-        <v>0.007300489826997365</v>
+        <v>0.00700996516223948</v>
       </c>
     </row>
     <row r="34">
@@ -3131,61 +3131,61 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5387040856238987</v>
+        <v>0.5349473716287773</v>
       </c>
       <c r="L34" t="n">
-        <v>0.450881926604315</v>
+        <v>0.5382437891085146</v>
       </c>
       <c r="M34" t="n">
-        <v>4.291280449636701</v>
+        <v>4.267183287460422</v>
       </c>
       <c r="N34" t="n">
-        <v>4.281735804523738</v>
+        <v>4.312129425377156</v>
       </c>
       <c r="O34" t="n">
-        <v>0.004690073035452948</v>
+        <v>0.006214857362383317</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01275303187543643</v>
+        <v>0.01699926117595317</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.003072390407171038</v>
+        <v>0.003612240519342102</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01470118427902963</v>
+        <v>0.01759639272267261</v>
       </c>
       <c r="S34" t="n">
-        <v>0.008497861375679708</v>
+        <v>0.01047895134576164</v>
       </c>
       <c r="T34" t="n">
-        <v>0.006428896915307041</v>
+        <v>0.009742875937494545</v>
       </c>
       <c r="U34" t="n">
-        <v>0.0470266747129684</v>
+        <v>0.08251836770906038</v>
       </c>
       <c r="V34" t="n">
-        <v>0.005846986622031445</v>
+        <v>0.005137753961292672</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01879655583935826</v>
+        <v>0.02269479885129614</v>
       </c>
       <c r="X34" t="n">
-        <v>0.007457564664721176</v>
+        <v>0.00896963025683536</v>
       </c>
     </row>
     <row r="35">
@@ -3211,61 +3211,61 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3025718444011018</v>
+        <v>0.2459581993328201</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2499236069255949</v>
+        <v>0.2359432290159188</v>
       </c>
       <c r="M35" t="n">
-        <v>4.05737490915139</v>
+        <v>3.975752990096821</v>
       </c>
       <c r="N35" t="n">
-        <v>4.15193336697933</v>
+        <v>4.147857086953065</v>
       </c>
       <c r="O35" t="n">
-        <v>0.001235491514101082</v>
+        <v>0.001238793578734914</v>
       </c>
       <c r="P35" t="n">
-        <v>0.03357969006695641</v>
+        <v>0.499999999994706</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.000607835107932592</v>
+        <v>0.0005745121579241243</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004849918034519818</v>
+        <v>0.004464426784697684</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0009582475394005796</v>
+        <v>0.0009130636002167316</v>
       </c>
       <c r="T35" t="n">
-        <v>0.002458002565470871</v>
+        <v>0.00249638531683662</v>
       </c>
       <c r="U35" t="n">
-        <v>12.26788287907425</v>
+        <v>6468.60806307083</v>
       </c>
       <c r="V35" t="n">
-        <v>0.002253364702528688</v>
+        <v>0.002162074040936976</v>
       </c>
       <c r="W35" t="n">
-        <v>0.02096471033507092</v>
+        <v>0.0264080285028549</v>
       </c>
       <c r="X35" t="n">
-        <v>0.00267476923513267</v>
+        <v>0.002533509250058015</v>
       </c>
     </row>
     <row r="36">
@@ -3291,61 +3291,61 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.432114221689511</v>
+        <v>0.3970681303962988</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3934889538239607</v>
+        <v>0.3691396770741446</v>
       </c>
       <c r="M36" t="n">
-        <v>4.321952334671811</v>
+        <v>4.31291763426113</v>
       </c>
       <c r="N36" t="n">
-        <v>4.315700192215298</v>
+        <v>4.307550674780784</v>
       </c>
       <c r="O36" t="n">
-        <v>0.001008408305604739</v>
+        <v>0.0009752856063394406</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002032393319238109</v>
+        <v>0.001885358814981861</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0004101598320585874</v>
+        <v>0.0003696677089741656</v>
       </c>
       <c r="R36" t="n">
-        <v>0.001946913991492018</v>
+        <v>0.001796481143817508</v>
       </c>
       <c r="S36" t="n">
-        <v>0.001319761917042878</v>
+        <v>0.001225826330714774</v>
       </c>
       <c r="T36" t="n">
-        <v>0.002451026684508723</v>
+        <v>0.002408295631550217</v>
       </c>
       <c r="U36" t="n">
-        <v>0.004383101792824889</v>
+        <v>0.004289421944219651</v>
       </c>
       <c r="V36" t="n">
-        <v>0.002570189462926131</v>
+        <v>0.002541248684783677</v>
       </c>
       <c r="W36" t="n">
-        <v>0.003645233782416663</v>
+        <v>0.003540194813886496</v>
       </c>
       <c r="X36" t="n">
-        <v>0.004543354136486776</v>
+        <v>0.00446015982795111</v>
       </c>
     </row>
     <row r="37">
@@ -3371,61 +3371,61 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1035375728459106</v>
+        <v>0.05755759486930409</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1171591017568475</v>
+        <v>0.07037544686481832</v>
       </c>
       <c r="M37" t="n">
-        <v>4.240813110988225</v>
+        <v>4.231556993851775</v>
       </c>
       <c r="N37" t="n">
-        <v>4.271074928022523</v>
+        <v>4.25944927929172</v>
       </c>
       <c r="O37" t="n">
-        <v>0.001425162358900785</v>
+        <v>0.001411953332965493</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0007042530275524824</v>
+        <v>0.0005308925374675324</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.001266376324922782</v>
+        <v>0.001238268956759675</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0008579992845053234</v>
+        <v>0.0007195752296837749</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002392319415189669</v>
+        <v>0.001941661451422511</v>
       </c>
       <c r="T37" t="n">
-        <v>0.003382033435560812</v>
+        <v>0.003388881794729776</v>
       </c>
       <c r="U37" t="n">
-        <v>0.001953206244000848</v>
+        <v>0.001732636046821254</v>
       </c>
       <c r="V37" t="n">
-        <v>0.003324412793488031</v>
+        <v>0.003259045859891605</v>
       </c>
       <c r="W37" t="n">
-        <v>0.002588786613463288</v>
+        <v>0.002435066960314566</v>
       </c>
       <c r="X37" t="n">
-        <v>0.005950532131247049</v>
+        <v>0.00495462571990293</v>
       </c>
     </row>
     <row r="38">
@@ -3451,61 +3451,61 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1433109613706779</v>
+        <v>0.08996212189252457</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1277231843256094</v>
+        <v>0.07845262483669468</v>
       </c>
       <c r="M38" t="n">
-        <v>4.158873949626578</v>
+        <v>4.142537911135626</v>
       </c>
       <c r="N38" t="n">
-        <v>4.19896969761463</v>
+        <v>4.181514285095943</v>
       </c>
       <c r="O38" t="n">
-        <v>0.001825414876281545</v>
+        <v>0.001821516998801657</v>
       </c>
       <c r="P38" t="n">
-        <v>0.0005234447571410045</v>
+        <v>0.0004545855591582402</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0008139357655750706</v>
+        <v>0.0007913467313133458</v>
       </c>
       <c r="R38" t="n">
-        <v>0.000482220560484867</v>
+        <v>0.0003414255621984318</v>
       </c>
       <c r="S38" t="n">
-        <v>0.0005737900523037063</v>
+        <v>5.769017423952701e-05</v>
       </c>
       <c r="T38" t="n">
-        <v>0.004255555693477111</v>
+        <v>0.004294365474760113</v>
       </c>
       <c r="U38" t="n">
-        <v>0.001644605051547562</v>
+        <v>0.001593772130123952</v>
       </c>
       <c r="V38" t="n">
-        <v>0.002641107026599577</v>
+        <v>0.002594381808410473</v>
       </c>
       <c r="W38" t="n">
-        <v>0.002168068381011788</v>
+        <v>0.002028927905630326</v>
       </c>
       <c r="X38" t="n">
-        <v>0.003515432887186348</v>
+        <v>0.002764382557497266</v>
       </c>
     </row>
     <row r="39">
@@ -3531,61 +3531,61 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1521632323991432</v>
+        <v>0.09663475671709176</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1365428260454886</v>
+        <v>0.08937829104078603</v>
       </c>
       <c r="M39" t="n">
-        <v>4.276604215929122</v>
+        <v>4.263201611065282</v>
       </c>
       <c r="N39" t="n">
-        <v>4.264390543388925</v>
+        <v>4.252803795564823</v>
       </c>
       <c r="O39" t="n">
-        <v>0.001637116370510771</v>
+        <v>0.001601926198531034</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0005290314786350071</v>
+        <v>0.0003366431932689329</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.001084462504970598</v>
+        <v>0.001056129011225323</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002336353455538666</v>
+        <v>0.002068451229250729</v>
       </c>
       <c r="S39" t="n">
-        <v>0.001427733491618876</v>
+        <v>0.001309882693735642</v>
       </c>
       <c r="T39" t="n">
-        <v>0.003254718186188554</v>
+        <v>0.003227767439206243</v>
       </c>
       <c r="U39" t="n">
-        <v>0.002493280819482371</v>
+        <v>0.002371673099018905</v>
       </c>
       <c r="V39" t="n">
-        <v>0.002868773500442054</v>
+        <v>0.00282758889230128</v>
       </c>
       <c r="W39" t="n">
-        <v>0.004050400060356956</v>
+        <v>0.003832823743408251</v>
       </c>
       <c r="X39" t="n">
-        <v>0.003026371867615176</v>
+        <v>0.002961679939955286</v>
       </c>
     </row>
     <row r="40">
@@ -3611,61 +3611,61 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.249459596754826</v>
+        <v>0.2447240331807525</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4069057434259198</v>
+        <v>0.3958448874977987</v>
       </c>
       <c r="M40" t="n">
-        <v>4.314959883928858</v>
+        <v>4.317329227224308</v>
       </c>
       <c r="N40" t="n">
-        <v>4.521452152850086</v>
+        <v>4.52264465750542</v>
       </c>
       <c r="O40" t="n">
-        <v>0.002929587345953262</v>
+        <v>0.002900555308689025</v>
       </c>
       <c r="P40" t="n">
-        <v>0.001974329128626674</v>
+        <v>0.001862701793821096</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.002552371033451315</v>
+        <v>0.002518427499829001</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002466699232687415</v>
+        <v>0.002414254251141706</v>
       </c>
       <c r="S40" t="n">
-        <v>0.05690397639444472</v>
+        <v>0.0547625456767057</v>
       </c>
       <c r="T40" t="n">
-        <v>0.004919915788111505</v>
+        <v>0.00487815636415582</v>
       </c>
       <c r="U40" t="n">
-        <v>0.003893531317131126</v>
+        <v>0.004104263592881701</v>
       </c>
       <c r="V40" t="n">
-        <v>0.005065691343410984</v>
+        <v>0.005131344331545673</v>
       </c>
       <c r="W40" t="n">
-        <v>0.003752724664824962</v>
+        <v>0.003810841685569103</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2746607808232225</v>
+        <v>0.2631683598299667</v>
       </c>
     </row>
     <row r="41">
@@ -3691,61 +3691,61 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2573692229621695</v>
+        <v>0.195223836174422</v>
       </c>
       <c r="L41" t="n">
-        <v>0.281650525074159</v>
+        <v>0.2298287918943051</v>
       </c>
       <c r="M41" t="n">
-        <v>4.427001742671981</v>
+        <v>4.426831872784585</v>
       </c>
       <c r="N41" t="n">
-        <v>4.510730549911854</v>
+        <v>4.510924526744252</v>
       </c>
       <c r="O41" t="n">
-        <v>0.0009500427217974113</v>
+        <v>0.0008928117249336103</v>
       </c>
       <c r="P41" t="n">
-        <v>0.001519139405170324</v>
+        <v>0.001200632270871777</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.0009880836577175927</v>
+        <v>0.0009565423617101247</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0009572303937104705</v>
+        <v>0.0008729991275740937</v>
       </c>
       <c r="S41" t="n">
-        <v>0.003909904020213783</v>
+        <v>0.003543875067036561</v>
       </c>
       <c r="T41" t="n">
-        <v>0.002069633840758412</v>
+        <v>0.002011491431704259</v>
       </c>
       <c r="U41" t="n">
-        <v>0.002810303417339061</v>
+        <v>0.002519416462177359</v>
       </c>
       <c r="V41" t="n">
-        <v>0.002236264509960483</v>
+        <v>0.002189925643314253</v>
       </c>
       <c r="W41" t="n">
-        <v>0.002145592981622896</v>
+        <v>0.002051471419447568</v>
       </c>
       <c r="X41" t="n">
-        <v>0.006854114611693964</v>
+        <v>0.006342029050505042</v>
       </c>
     </row>
     <row r="42">
@@ -3771,61 +3771,61 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3161275944552756</v>
+        <v>0.1311334681965219</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4156921543838948</v>
+        <v>0.3656937566800134</v>
       </c>
       <c r="M42" t="n">
-        <v>4.505860970347477</v>
+        <v>2.432463726727812</v>
       </c>
       <c r="N42" t="n">
-        <v>4.560556190252406</v>
+        <v>4.467596704336187</v>
       </c>
       <c r="O42" t="n">
-        <v>0.003651455768320976</v>
+        <v>0.003523386233719892</v>
       </c>
       <c r="P42" t="n">
-        <v>0.002769108169709419</v>
+        <v>0.002120537545429617</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.004448149246375137</v>
+        <v>0.004355639034052798</v>
       </c>
       <c r="R42" t="n">
-        <v>0.003022131350502476</v>
+        <v>0.002787708065175892</v>
       </c>
       <c r="S42" t="n">
-        <v>1e-05</v>
+        <v>0.4576334326708364</v>
       </c>
       <c r="T42" t="n">
-        <v>0.0105276764798582</v>
+        <v>0.007749657453849333</v>
       </c>
       <c r="U42" t="n">
-        <v>0.026703626477766</v>
+        <v>0.008884926362419153</v>
       </c>
       <c r="V42" t="n">
-        <v>0.01321111169007812</v>
+        <v>0.01214791455631397</v>
       </c>
       <c r="W42" t="n">
-        <v>0.01185435456345314</v>
+        <v>0.006322582828772882</v>
       </c>
       <c r="X42" t="n">
-        <v>2.996876294705864</v>
+        <v>3.352188405978778e-09</v>
       </c>
     </row>
     <row r="43">
@@ -3851,61 +3851,61 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.214561338787775</v>
+        <v>0.1864807199699899</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3895964545304603</v>
+        <v>0.3818637018680048</v>
       </c>
       <c r="M43" t="n">
-        <v>3.957269318509153</v>
+        <v>3.965151146825701</v>
       </c>
       <c r="N43" t="n">
-        <v>4.263489611510439</v>
+        <v>4.256611868595258</v>
       </c>
       <c r="O43" t="n">
-        <v>0.01674700268598306</v>
+        <v>0.01741878548928298</v>
       </c>
       <c r="P43" t="n">
-        <v>0.009942437477260209</v>
+        <v>0.00928726170015853</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.02007292774607138</v>
+        <v>0.02093302296108103</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02293338784084878</v>
+        <v>0.02089196513303763</v>
       </c>
       <c r="S43" t="n">
-        <v>0.06360618232373537</v>
+        <v>0.06039259869751168</v>
       </c>
       <c r="T43" t="n">
-        <v>0.02905519193447997</v>
+        <v>0.02808654891663384</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02060004422470382</v>
+        <v>0.02040412833310027</v>
       </c>
       <c r="V43" t="n">
-        <v>0.04696592993418618</v>
+        <v>0.04948955257036129</v>
       </c>
       <c r="W43" t="n">
-        <v>0.04776082233542486</v>
+        <v>0.05032619788391101</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1734825633000293</v>
+        <v>0.164557882784434</v>
       </c>
     </row>
     <row r="44">
@@ -3931,61 +3931,61 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1729821644702371</v>
+        <v>0.1160040171888872</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3961689454705551</v>
+        <v>0.3741130630197994</v>
       </c>
       <c r="M44" t="n">
-        <v>4.220618689085988</v>
+        <v>4.221992695387505</v>
       </c>
       <c r="N44" t="n">
-        <v>4.393130684049197</v>
+        <v>4.382687577846458</v>
       </c>
       <c r="O44" t="n">
-        <v>0.02583827132454846</v>
+        <v>0.02503885560291694</v>
       </c>
       <c r="P44" t="n">
-        <v>0.01266471581677057</v>
+        <v>0.01145670772608285</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02392022453591427</v>
+        <v>0.02412383864671729</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01203067736005225</v>
+        <v>0.01083471410970834</v>
       </c>
       <c r="S44" t="n">
-        <v>0.02332355470578531</v>
+        <v>0.02034455942920898</v>
       </c>
       <c r="T44" t="n">
-        <v>0.05348613224703609</v>
+        <v>0.05262933432759823</v>
       </c>
       <c r="U44" t="n">
-        <v>0.02241826353741333</v>
+        <v>0.02129510617980311</v>
       </c>
       <c r="V44" t="n">
-        <v>0.05596917486159735</v>
+        <v>0.05649983870957816</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02292320361049745</v>
+        <v>0.02225560953875284</v>
       </c>
       <c r="X44" t="n">
-        <v>0.04711065153991716</v>
+        <v>0.04259830562584577</v>
       </c>
     </row>
     <row r="45">
@@ -4011,61 +4011,61 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.402064738426252</v>
+        <v>0.3599855396326003</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3475433572858478</v>
+        <v>0.4783661489839898</v>
       </c>
       <c r="M45" t="n">
-        <v>4.273822963139304</v>
+        <v>4.246879291334123</v>
       </c>
       <c r="N45" t="n">
-        <v>4.372632385419013</v>
+        <v>4.418143141072385</v>
       </c>
       <c r="O45" t="n">
-        <v>0.07135366522764755</v>
+        <v>0.07721318724752355</v>
       </c>
       <c r="P45" t="n">
-        <v>0.08746748301265329</v>
+        <v>0.08165383378851238</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.06618598023413179</v>
+        <v>0.05374227184681066</v>
       </c>
       <c r="R45" t="n">
-        <v>0.1047651963502601</v>
+        <v>0.09354469738887861</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1300631539439227</v>
+        <v>0.1170555418879767</v>
       </c>
       <c r="T45" t="n">
-        <v>0.2005940886136379</v>
+        <v>0.2387521997243088</v>
       </c>
       <c r="U45" t="n">
-        <v>0.2430199268960533</v>
+        <v>0.2281067442919686</v>
       </c>
       <c r="V45" t="n">
-        <v>0.2149393707298246</v>
+        <v>0.1575811073357216</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2743122140323959</v>
+        <v>0.2510208253819348</v>
       </c>
       <c r="X45" t="n">
-        <v>0.4947255431501673</v>
+        <v>0.428954894954261</v>
       </c>
     </row>
     <row r="46">
@@ -4091,61 +4091,61 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4152342674066459</v>
+        <v>0.4033453330186448</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3811288988599959</v>
+        <v>0.4829174272706265</v>
       </c>
       <c r="M46" t="n">
-        <v>3.736658907187545</v>
+        <v>3.778791310898719</v>
       </c>
       <c r="N46" t="n">
-        <v>4.494678572468655</v>
+        <v>4.476138985560363</v>
       </c>
       <c r="O46" t="n">
-        <v>0.05363566340805416</v>
+        <v>0.05723791518464611</v>
       </c>
       <c r="P46" t="n">
-        <v>0.03396261609905674</v>
+        <v>0.03626836816374761</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02748023772924122</v>
+        <v>0.0260050953034355</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0353713838733486</v>
+        <v>0.03759145692939202</v>
       </c>
       <c r="S46" t="n">
-        <v>0.1907982781147629</v>
+        <v>0.1835181336955814</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1290100766926578</v>
+        <v>0.1426681598118602</v>
       </c>
       <c r="U46" t="n">
-        <v>0.06374704627368719</v>
+        <v>0.06909445818938392</v>
       </c>
       <c r="V46" t="n">
-        <v>0.05439885402576789</v>
+        <v>0.04936457394642008</v>
       </c>
       <c r="W46" t="n">
-        <v>0.0542414767917497</v>
+        <v>0.05987798004059705</v>
       </c>
       <c r="X46" t="n">
-        <v>2.18989719978157</v>
+        <v>1.947164228176619</v>
       </c>
     </row>
     <row r="47">
@@ -4171,61 +4171,61 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.249759804799666</v>
+        <v>0.1903563654068834</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4066190590329566</v>
+        <v>0.3842019128456324</v>
       </c>
       <c r="M47" t="n">
-        <v>4.226749871470481</v>
+        <v>4.218169191500397</v>
       </c>
       <c r="N47" t="n">
-        <v>4.358112882208157</v>
+        <v>4.348273340283221</v>
       </c>
       <c r="O47" t="n">
-        <v>0.02408535121683737</v>
+        <v>0.02388964727333836</v>
       </c>
       <c r="P47" t="n">
-        <v>0.01273485839807877</v>
+        <v>0.0117109230293584</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.02262674046730047</v>
+        <v>0.0220934122447036</v>
       </c>
       <c r="R47" t="n">
-        <v>0.01773005861029248</v>
+        <v>0.01571826113479599</v>
       </c>
       <c r="S47" t="n">
-        <v>0.02607332262035277</v>
+        <v>0.02286303104447078</v>
       </c>
       <c r="T47" t="n">
-        <v>0.04649709426130562</v>
+        <v>0.04717966769565809</v>
       </c>
       <c r="U47" t="n">
-        <v>0.02148883897366578</v>
+        <v>0.02068033485131231</v>
       </c>
       <c r="V47" t="n">
-        <v>0.05469316239144191</v>
+        <v>0.05314571731651224</v>
       </c>
       <c r="W47" t="n">
-        <v>0.03119668402963288</v>
+        <v>0.03076133595508825</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04818002473516954</v>
+        <v>0.04606634081454698</v>
       </c>
     </row>
     <row r="48">
@@ -4251,61 +4251,61 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.112812893274769</v>
+        <v>0.06980095781629543</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4734586201414115</v>
+        <v>0.4919074574683899</v>
       </c>
       <c r="M48" t="n">
-        <v>3.689594567822128</v>
+        <v>3.762510994332883</v>
       </c>
       <c r="N48" t="n">
-        <v>4.336928262298008</v>
+        <v>4.339334064813332</v>
       </c>
       <c r="O48" t="n">
-        <v>0.02559752403332129</v>
+        <v>0.02584743655599214</v>
       </c>
       <c r="P48" t="n">
-        <v>0.03156462700033911</v>
+        <v>0.03165177608440705</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.05520509248539819</v>
+        <v>0.06691184864991848</v>
       </c>
       <c r="R48" t="n">
-        <v>0.03932594497329257</v>
+        <v>0.04004293311549639</v>
       </c>
       <c r="S48" t="n">
-        <v>0.1975976100558738</v>
+        <v>0.1913617279317552</v>
       </c>
       <c r="T48" t="n">
-        <v>0.04776671399339266</v>
+        <v>0.04933607593909337</v>
       </c>
       <c r="U48" t="n">
-        <v>0.06003374000187614</v>
+        <v>0.05933650533204041</v>
       </c>
       <c r="V48" t="n">
-        <v>0.1240898913214311</v>
+        <v>0.1329202056380749</v>
       </c>
       <c r="W48" t="n">
-        <v>0.07346333480786012</v>
+        <v>0.06809056873402429</v>
       </c>
       <c r="X48" t="n">
-        <v>3.650187926655053</v>
+        <v>3.287452784980827</v>
       </c>
     </row>
     <row r="49">
@@ -4331,61 +4331,61 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3620994881251263</v>
+        <v>0.3226065171575305</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4642049442610478</v>
+        <v>0.4685201933535184</v>
       </c>
       <c r="M49" t="n">
-        <v>4.033112792883243</v>
+        <v>4.046686012503025</v>
       </c>
       <c r="N49" t="n">
-        <v>4.397384474855732</v>
+        <v>4.395231242972984</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0161874793892966</v>
+        <v>0.01626222066172079</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01009976348879426</v>
+        <v>0.009895613527908272</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01862565673184269</v>
+        <v>0.01885785546158392</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01790466064962356</v>
+        <v>0.01777161017576374</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09152580202954097</v>
+        <v>0.08762655475589139</v>
       </c>
       <c r="T49" t="n">
-        <v>0.02868247334494153</v>
+        <v>0.02883306571836421</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01449451821969203</v>
+        <v>0.01519620633460224</v>
       </c>
       <c r="V49" t="n">
-        <v>0.04102217925389352</v>
+        <v>0.04258675585440633</v>
       </c>
       <c r="W49" t="n">
-        <v>0.02774209885819313</v>
+        <v>0.02914151221832841</v>
       </c>
       <c r="X49" t="n">
-        <v>0.3134519477737845</v>
+        <v>0.2951193988666913</v>
       </c>
     </row>
     <row r="50">
@@ -4411,61 +4411,61 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5100697585861687</v>
+        <v>0.4990340157055358</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5539703020498961</v>
+        <v>0.5576546440713213</v>
       </c>
       <c r="M50" t="n">
-        <v>4.291959939524077</v>
+        <v>4.286590071874298</v>
       </c>
       <c r="N50" t="n">
-        <v>4.521509823790423</v>
+        <v>4.457199233417131</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0644694333215249</v>
+        <v>0.06519054081141964</v>
       </c>
       <c r="P50" t="n">
-        <v>0.05991636849154471</v>
+        <v>0.06145302556558209</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.0604794949816118</v>
+        <v>0.0607507902343687</v>
       </c>
       <c r="R50" t="n">
-        <v>0.03297584830203118</v>
+        <v>0.03420241799909936</v>
       </c>
       <c r="S50" t="n">
-        <v>0.004409774390758087</v>
+        <v>0.01150379558953721</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1964375030733685</v>
+        <v>0.2140719229504228</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2170547427926068</v>
+        <v>0.2184813177742955</v>
       </c>
       <c r="V50" t="n">
-        <v>0.2283578671378693</v>
+        <v>0.2209509175972313</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1221695992670814</v>
+        <v>0.1322486686835949</v>
       </c>
       <c r="X50" t="n">
-        <v>25.76750488950472</v>
+        <v>16.25084686193938</v>
       </c>
     </row>
     <row r="51">
@@ -4491,61 +4491,61 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4766078924922043</v>
+        <v>0.4747357510883822</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5522904382153022</v>
+        <v>0.5586303904736262</v>
       </c>
       <c r="M51" t="n">
-        <v>3.851203782657342</v>
+        <v>3.849426342197498</v>
       </c>
       <c r="N51" t="n">
-        <v>4.429547288090052</v>
+        <v>4.43022679476616</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05426323129579202</v>
+        <v>0.05454904850794997</v>
       </c>
       <c r="P51" t="n">
-        <v>0.04064371055427094</v>
+        <v>0.04120494255466624</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1267044319482724</v>
+        <v>0.127982663838095</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0629569471919369</v>
+        <v>0.06373674153799248</v>
       </c>
       <c r="S51" t="n">
-        <v>0.2143110993727872</v>
+        <v>0.2175562920146673</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1308918225289418</v>
+        <v>0.1321140241879405</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08068333853008874</v>
+        <v>0.08216689881997412</v>
       </c>
       <c r="V51" t="n">
-        <v>0.2328825484903567</v>
+        <v>0.2283350856669356</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1170864230665695</v>
+        <v>0.1193181342579305</v>
       </c>
       <c r="X51" t="n">
-        <v>2.357640730774623</v>
+        <v>2.407129196586237</v>
       </c>
     </row>
     <row r="52">
@@ -4571,61 +4571,61 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1562936953832578</v>
+        <v>0.1003996704124989</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2431379390752078</v>
+        <v>0.1776022826614817</v>
       </c>
       <c r="M52" t="n">
-        <v>4.255272484088167</v>
+        <v>4.241864768630935</v>
       </c>
       <c r="N52" t="n">
-        <v>4.298538256987295</v>
+        <v>4.28178334926914</v>
       </c>
       <c r="O52" t="n">
-        <v>0.008060321128216426</v>
+        <v>0.007696363224374694</v>
       </c>
       <c r="P52" t="n">
-        <v>0.003790983972572807</v>
+        <v>0.003093509744386538</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.008374729883284119</v>
+        <v>0.007832644084126341</v>
       </c>
       <c r="R52" t="n">
-        <v>0.004452670947736255</v>
+        <v>0.003482558159816543</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01360188882076303</v>
+        <v>0.009738484203240635</v>
       </c>
       <c r="T52" t="n">
-        <v>0.0143470719591339</v>
+        <v>0.01397451495751428</v>
       </c>
       <c r="U52" t="n">
-        <v>0.009087880260668903</v>
+        <v>0.008342393898339309</v>
       </c>
       <c r="V52" t="n">
-        <v>0.01671713507210094</v>
+        <v>0.0154960188473149</v>
       </c>
       <c r="W52" t="n">
-        <v>0.0118800269569116</v>
+        <v>0.0106940368772496</v>
       </c>
       <c r="X52" t="n">
-        <v>0.03680078305480584</v>
+        <v>0.03035286461782028</v>
       </c>
     </row>
     <row r="53">
@@ -4651,61 +4651,61 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3358214977156689</v>
+        <v>0.2783551458295477</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2368791358636469</v>
+        <v>0.2433294584670261</v>
       </c>
       <c r="M53" t="n">
-        <v>4.45233489759441</v>
+        <v>4.435198931413451</v>
       </c>
       <c r="N53" t="n">
-        <v>4.414240723809666</v>
+        <v>4.415546712378527</v>
       </c>
       <c r="O53" t="n">
-        <v>0.01770505992205451</v>
+        <v>0.01845554213904164</v>
       </c>
       <c r="P53" t="n">
-        <v>0.009821686894824383</v>
+        <v>0.009212601705791103</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01035401649560193</v>
+        <v>0.009779086993975726</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02220011370049087</v>
+        <v>0.02092969296106889</v>
       </c>
       <c r="S53" t="n">
-        <v>0.07202129164220857</v>
+        <v>0.0608296337111105</v>
       </c>
       <c r="T53" t="n">
-        <v>0.02974206412240668</v>
+        <v>0.03288668261337075</v>
       </c>
       <c r="U53" t="n">
-        <v>0.01508960660727301</v>
+        <v>0.01444955075999273</v>
       </c>
       <c r="V53" t="n">
-        <v>0.01962137590998968</v>
+        <v>0.01857969413767693</v>
       </c>
       <c r="W53" t="n">
-        <v>0.03754169458747039</v>
+        <v>0.03708161084141964</v>
       </c>
       <c r="X53" t="n">
-        <v>0.09576922539061115</v>
+        <v>0.08422742951966675</v>
       </c>
     </row>
     <row r="54">
@@ -4731,61 +4731,61 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2232363824600347</v>
+        <v>0.1652005085621645</v>
       </c>
       <c r="L54" t="n">
-        <v>0.438351402939473</v>
+        <v>0.4251644770650234</v>
       </c>
       <c r="M54" t="n">
-        <v>4.144200181763916</v>
+        <v>4.147708344073652</v>
       </c>
       <c r="N54" t="n">
-        <v>4.316666210315921</v>
+        <v>4.30350362114648</v>
       </c>
       <c r="O54" t="n">
-        <v>0.02028928225939141</v>
+        <v>0.01988971337232071</v>
       </c>
       <c r="P54" t="n">
-        <v>0.007541285606136035</v>
+        <v>0.006871590546431604</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.02327025920945999</v>
+        <v>0.02420750782417868</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009540216235494416</v>
+        <v>0.008636321122728727</v>
       </c>
       <c r="S54" t="n">
-        <v>0.02380575436381814</v>
+        <v>0.02196053609339923</v>
       </c>
       <c r="T54" t="n">
-        <v>0.03922353821965439</v>
+        <v>0.03873810134905034</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01306399661092278</v>
+        <v>0.0131498431421626</v>
       </c>
       <c r="V54" t="n">
-        <v>0.05468647429942235</v>
+        <v>0.05771223906453791</v>
       </c>
       <c r="W54" t="n">
-        <v>0.01816095842314383</v>
+        <v>0.01867699465030327</v>
       </c>
       <c r="X54" t="n">
-        <v>0.0441391381239669</v>
+        <v>0.04224106197842584</v>
       </c>
     </row>
     <row r="55">
@@ -4811,61 +4811,61 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.196852432134677</v>
+        <v>0.1364807019502954</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4691666266486137</v>
+        <v>0.4788524816569951</v>
       </c>
       <c r="M55" t="n">
-        <v>4.361472218356489</v>
+        <v>4.361516370208551</v>
       </c>
       <c r="N55" t="n">
-        <v>4.402641732322775</v>
+        <v>4.403331791201476</v>
       </c>
       <c r="O55" t="n">
-        <v>0.01512321618874698</v>
+        <v>0.01535412715228182</v>
       </c>
       <c r="P55" t="n">
-        <v>0.008674562808153093</v>
+        <v>0.008608147286653035</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.02961247541669653</v>
+        <v>0.03600947778639862</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01445354587240994</v>
+        <v>0.01444448331432654</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01441899610753118</v>
+        <v>0.01435576842059705</v>
       </c>
       <c r="T55" t="n">
-        <v>0.02662204894152851</v>
+        <v>0.02742936421856233</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01272464416113266</v>
+        <v>0.01265928261410693</v>
       </c>
       <c r="V55" t="n">
-        <v>0.05656063820735676</v>
+        <v>0.06596761746265824</v>
       </c>
       <c r="W55" t="n">
-        <v>0.02038180191819067</v>
+        <v>0.02057914882484339</v>
       </c>
       <c r="X55" t="n">
-        <v>0.02523082379732405</v>
+        <v>0.02469106917293103</v>
       </c>
     </row>
     <row r="56">
@@ -4891,61 +4891,61 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2062853367551514</v>
+        <v>0.150223218442535</v>
       </c>
       <c r="L56" t="n">
-        <v>0.389216721446197</v>
+        <v>0.3808533813344335</v>
       </c>
       <c r="M56" t="n">
-        <v>4.024244761351998</v>
+        <v>4.031079539857037</v>
       </c>
       <c r="N56" t="n">
-        <v>4.337611414464551</v>
+        <v>4.33111338911064</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01393463174913516</v>
+        <v>0.01365934204441689</v>
       </c>
       <c r="P56" t="n">
-        <v>0.007758396099700073</v>
+        <v>0.00732117792901337</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01799209052484299</v>
+        <v>0.01911815877714705</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01437359240774169</v>
+        <v>0.0135381952528184</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04448511045302854</v>
+        <v>0.04271879795866213</v>
       </c>
       <c r="T56" t="n">
-        <v>0.0254295940444287</v>
+        <v>0.02516393487714456</v>
       </c>
       <c r="U56" t="n">
-        <v>0.01402327458422527</v>
+        <v>0.0139242004093816</v>
       </c>
       <c r="V56" t="n">
-        <v>0.04295491789855975</v>
+        <v>0.04645829957072822</v>
       </c>
       <c r="W56" t="n">
-        <v>0.02516004420962444</v>
+        <v>0.0253620002026916</v>
       </c>
       <c r="X56" t="n">
-        <v>0.1114880976299194</v>
+        <v>0.1080049263837845</v>
       </c>
     </row>
     <row r="57">
@@ -4971,61 +4971,61 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3797827501136171</v>
+        <v>0.336114860226541</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4584475774641634</v>
+        <v>0.4552752039430819</v>
       </c>
       <c r="M57" t="n">
-        <v>4.247766393668665</v>
+        <v>4.246456518302081</v>
       </c>
       <c r="N57" t="n">
-        <v>4.374906267354293</v>
+        <v>4.371571953182547</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02048295023548657</v>
+        <v>0.02054016343274672</v>
       </c>
       <c r="P57" t="n">
-        <v>0.008175415431832677</v>
+        <v>0.007959635531833945</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01662787973941763</v>
+        <v>0.01638030107516865</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01377617510323336</v>
+        <v>0.01336152111759987</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02115101029095347</v>
+        <v>0.02006014406651316</v>
       </c>
       <c r="T57" t="n">
-        <v>0.03926956885353038</v>
+        <v>0.0398681910123069</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01315596784326675</v>
+        <v>0.01308319382815353</v>
       </c>
       <c r="V57" t="n">
-        <v>0.03491681451251267</v>
+        <v>0.03511668678756711</v>
       </c>
       <c r="W57" t="n">
-        <v>0.02011532732068335</v>
+        <v>0.02064630885425539</v>
       </c>
       <c r="X57" t="n">
-        <v>0.03268202368378623</v>
+        <v>0.03206343586212988</v>
       </c>
     </row>
     <row r="58">
@@ -5051,61 +5051,61 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2024072301870912</v>
+        <v>0.1666120314608137</v>
       </c>
       <c r="L58" t="n">
-        <v>0.507936558445012</v>
+        <v>0.5098746874725855</v>
       </c>
       <c r="M58" t="n">
-        <v>4.10470435677508</v>
+        <v>4.116850885198406</v>
       </c>
       <c r="N58" t="n">
-        <v>4.418189908426267</v>
+        <v>4.418557517915638</v>
       </c>
       <c r="O58" t="n">
-        <v>0.03934186555252187</v>
+        <v>0.04064248904105216</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01020014335745532</v>
+        <v>0.009468112963776623</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.04429254835499982</v>
+        <v>0.05035695827195752</v>
       </c>
       <c r="R58" t="n">
-        <v>0.008998478270909412</v>
+        <v>0.008645121709449179</v>
       </c>
       <c r="S58" t="n">
-        <v>0.04767151577188267</v>
+        <v>0.04631045476412002</v>
       </c>
       <c r="T58" t="n">
-        <v>0.08723853830465315</v>
+        <v>0.09372273088888684</v>
       </c>
       <c r="U58" t="n">
-        <v>0.01724588924986532</v>
+        <v>0.01523593911997508</v>
       </c>
       <c r="V58" t="n">
-        <v>0.1163091016780616</v>
+        <v>0.1350167328115132</v>
       </c>
       <c r="W58" t="n">
-        <v>0.018126544495969</v>
+        <v>0.01867766348502505</v>
       </c>
       <c r="X58" t="n">
-        <v>0.09991102966217559</v>
+        <v>0.1007749065461759</v>
       </c>
     </row>
     <row r="59">
@@ -5131,61 +5131,61 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4652114978160279</v>
+        <v>0.4445932488388378</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5160146015280053</v>
+        <v>0.5307886334085006</v>
       </c>
       <c r="M59" t="n">
-        <v>4.189896485281355</v>
+        <v>4.18553294972197</v>
       </c>
       <c r="N59" t="n">
-        <v>4.385968736067589</v>
+        <v>4.387099489018315</v>
       </c>
       <c r="O59" t="n">
-        <v>0.01039003559942345</v>
+        <v>0.01076952506511486</v>
       </c>
       <c r="P59" t="n">
-        <v>0.004090829711645934</v>
+        <v>0.00417709220960882</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.008140012196128747</v>
+        <v>0.007500892399696781</v>
       </c>
       <c r="R59" t="n">
-        <v>0.005967987584729168</v>
+        <v>0.006025281602482127</v>
       </c>
       <c r="S59" t="n">
-        <v>0.00687699182284492</v>
+        <v>0.006865843552493413</v>
       </c>
       <c r="T59" t="n">
-        <v>0.01724182448402028</v>
+        <v>0.01821453852289469</v>
       </c>
       <c r="U59" t="n">
-        <v>0.00502919546687001</v>
+        <v>0.00514879276089495</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01234045870613052</v>
+        <v>0.01108722561313881</v>
       </c>
       <c r="W59" t="n">
-        <v>0.005794323939093651</v>
+        <v>0.005996344815215071</v>
       </c>
       <c r="X59" t="n">
-        <v>0.006484472294282609</v>
+        <v>0.006540979989240953</v>
       </c>
     </row>
     <row r="60">
@@ -5211,61 +5211,61 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3216419994495925</v>
+        <v>0.271635444752685</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2754910818037129</v>
+        <v>0.2195716630807835</v>
       </c>
       <c r="M60" t="n">
-        <v>4.066724723170381</v>
+        <v>4.049738163537739</v>
       </c>
       <c r="N60" t="n">
-        <v>4.195277617408031</v>
+        <v>4.172347246401958</v>
       </c>
       <c r="O60" t="n">
-        <v>0.002206963725161294</v>
+        <v>0.00241039706945474</v>
       </c>
       <c r="P60" t="n">
-        <v>0.001742623613483473</v>
+        <v>0.001473172287991899</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.001144671944644499</v>
+        <v>0.001046641284367262</v>
       </c>
       <c r="R60" t="n">
-        <v>0.001733827611514837</v>
+        <v>0.001440471365648423</v>
       </c>
       <c r="S60" t="n">
-        <v>0.004802679878084692</v>
+        <v>0.004332077227352854</v>
       </c>
       <c r="T60" t="n">
-        <v>0.003094441657613748</v>
+        <v>0.00343596475182354</v>
       </c>
       <c r="U60" t="n">
-        <v>0.002652182332641902</v>
+        <v>0.002461851165627571</v>
       </c>
       <c r="V60" t="n">
-        <v>0.002224462588535324</v>
+        <v>0.002115391003003984</v>
       </c>
       <c r="W60" t="n">
-        <v>0.00243026684505122</v>
+        <v>0.002248323527566715</v>
       </c>
       <c r="X60" t="n">
-        <v>0.005635145456089533</v>
+        <v>0.005208112915690799</v>
       </c>
     </row>
     <row r="61">
@@ -5291,61 +5291,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.354482847122061</v>
+        <v>0.2900866812720037</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3244785466221577</v>
+        <v>0.323857556250595</v>
       </c>
       <c r="M61" t="n">
-        <v>3.865370088861562</v>
+        <v>3.873303134771478</v>
       </c>
       <c r="N61" t="n">
-        <v>4.234157641775879</v>
+        <v>4.243682570304977</v>
       </c>
       <c r="O61" t="n">
-        <v>0.004486311801617381</v>
+        <v>0.005960388313082679</v>
       </c>
       <c r="P61" t="n">
-        <v>0.004907768421651384</v>
+        <v>0.004799821715288924</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.002674838902088276</v>
+        <v>0.00231021084931946</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01105809474188295</v>
+        <v>0.01060275191942986</v>
       </c>
       <c r="S61" t="n">
-        <v>0.03381046398011307</v>
+        <v>0.03450475871076032</v>
       </c>
       <c r="T61" t="n">
-        <v>0.00546159375987806</v>
+        <v>0.008109858456517724</v>
       </c>
       <c r="U61" t="n">
-        <v>0.006491388103193359</v>
+        <v>0.00770600540664914</v>
       </c>
       <c r="V61" t="n">
-        <v>0.004320380904508562</v>
+        <v>0.003926094113462543</v>
       </c>
       <c r="W61" t="n">
-        <v>0.0106746514863673</v>
+        <v>0.01211066898454771</v>
       </c>
       <c r="X61" t="n">
-        <v>0.1664844130582454</v>
+        <v>0.1773794890066035</v>
       </c>
     </row>
     <row r="62">
@@ -5371,61 +5371,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.08024552226375803</v>
+        <v>0.09212125147723835</v>
       </c>
       <c r="L62" t="n">
-        <v>0.1392221578642731</v>
+        <v>0.189855916067165</v>
       </c>
       <c r="M62" t="n">
-        <v>4.141186837809406</v>
+        <v>4.146801828112358</v>
       </c>
       <c r="N62" t="n">
-        <v>4.16228236876073</v>
+        <v>4.175679773103433</v>
       </c>
       <c r="O62" t="n">
-        <v>0.006338983842136731</v>
+        <v>0.00642409313329077</v>
       </c>
       <c r="P62" t="n">
-        <v>0.001638996376209123</v>
+        <v>0.001922635116616095</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.002179325799596911</v>
+        <v>0.002222936836126821</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01065740027644142</v>
+        <v>0.01111965405443527</v>
       </c>
       <c r="S62" t="n">
-        <v>0.00849635762027299</v>
+        <v>0.008659522669504276</v>
       </c>
       <c r="T62" t="n">
-        <v>0.009719187108412818</v>
+        <v>0.009778956087984779</v>
       </c>
       <c r="U62" t="n">
-        <v>0.004734018527882065</v>
+        <v>0.005520713691236695</v>
       </c>
       <c r="V62" t="n">
-        <v>0.00406128002116417</v>
+        <v>0.004106740768791954</v>
       </c>
       <c r="W62" t="n">
-        <v>0.01960437973310001</v>
+        <v>0.02089280612300358</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01846663057659724</v>
+        <v>0.01880655760718389</v>
       </c>
     </row>
     <row r="63">
@@ -5451,61 +5451,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2554525714322201</v>
+        <v>0.245877187307462</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2875137900802257</v>
+        <v>0.313550426332836</v>
       </c>
       <c r="M63" t="n">
-        <v>3.980842593650126</v>
+        <v>3.984786969934592</v>
       </c>
       <c r="N63" t="n">
-        <v>4.218656340158622</v>
+        <v>4.225517476130906</v>
       </c>
       <c r="O63" t="n">
-        <v>0.004593948628447727</v>
+        <v>0.00515446795675337</v>
       </c>
       <c r="P63" t="n">
-        <v>0.003745692977553801</v>
+        <v>0.003947941139965883</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.002152861338250084</v>
+        <v>0.002076199763584538</v>
       </c>
       <c r="R63" t="n">
-        <v>0.007671842901053133</v>
+        <v>0.007783322830410568</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01603396267965642</v>
+        <v>0.01591247477198095</v>
       </c>
       <c r="T63" t="n">
-        <v>0.006209838537634856</v>
+        <v>0.007167537500511821</v>
       </c>
       <c r="U63" t="n">
-        <v>0.006571206873980848</v>
+        <v>0.007670289538665786</v>
       </c>
       <c r="V63" t="n">
-        <v>0.00382182444712029</v>
+        <v>0.003802333649348559</v>
       </c>
       <c r="W63" t="n">
-        <v>0.0121131087154823</v>
+        <v>0.01367783917827519</v>
       </c>
       <c r="X63" t="n">
-        <v>0.03394988290115274</v>
+        <v>0.03352942071505474</v>
       </c>
     </row>
     <row r="64">
@@ -5531,61 +5531,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1997197132401451</v>
+        <v>0.2058383658046032</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2906700349031219</v>
+        <v>0.3285575301317374</v>
       </c>
       <c r="M64" t="n">
-        <v>3.711467818595111</v>
+        <v>3.788363809657385</v>
       </c>
       <c r="N64" t="n">
-        <v>4.231444659658678</v>
+        <v>4.244600175152009</v>
       </c>
       <c r="O64" t="n">
-        <v>0.005600408832748029</v>
+        <v>0.00605749219639165</v>
       </c>
       <c r="P64" t="n">
-        <v>0.003877737396421357</v>
+        <v>0.004067448371676193</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.003663313041527408</v>
+        <v>0.003454545497650833</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01809675590385839</v>
+        <v>0.01771690155987781</v>
       </c>
       <c r="S64" t="n">
-        <v>0.05465902596931093</v>
+        <v>0.04742439877312414</v>
       </c>
       <c r="T64" t="n">
-        <v>0.007725154047102905</v>
+        <v>0.008452871539548034</v>
       </c>
       <c r="U64" t="n">
-        <v>0.006848208038601378</v>
+        <v>0.007450338836665028</v>
       </c>
       <c r="V64" t="n">
-        <v>0.006111297688043894</v>
+        <v>0.005865446076147012</v>
       </c>
       <c r="W64" t="n">
-        <v>0.02744947840044985</v>
+        <v>0.0279817694930046</v>
       </c>
       <c r="X64" t="n">
-        <v>0.9260645314559061</v>
+        <v>0.6231850582107904</v>
       </c>
     </row>
     <row r="65">
@@ -5611,61 +5611,61 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3034647984070029</v>
+        <v>0.2883423509517015</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3735138515229626</v>
+        <v>0.3981379177833136</v>
       </c>
       <c r="M65" t="n">
-        <v>3.907603328633307</v>
+        <v>3.920690783523073</v>
       </c>
       <c r="N65" t="n">
-        <v>4.262643286609993</v>
+        <v>4.27148345131883</v>
       </c>
       <c r="O65" t="n">
-        <v>0.005556145964231304</v>
+        <v>0.006180367812275497</v>
       </c>
       <c r="P65" t="n">
-        <v>0.005908824591350251</v>
+        <v>0.005991127193581308</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.004380344982140424</v>
+        <v>0.004076093396221839</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01092469085104699</v>
+        <v>0.0108861917045741</v>
       </c>
       <c r="S65" t="n">
-        <v>0.03266462076303852</v>
+        <v>0.03138461514253871</v>
       </c>
       <c r="T65" t="n">
-        <v>0.007091044759905106</v>
+        <v>0.007996695758740133</v>
       </c>
       <c r="U65" t="n">
-        <v>0.009387503067923306</v>
+        <v>0.01091714332908706</v>
       </c>
       <c r="V65" t="n">
-        <v>0.007225661420476604</v>
+        <v>0.00714089121683891</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01354373210782792</v>
+        <v>0.0164340226247054</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1333542129980715</v>
+        <v>0.1231474436160686</v>
       </c>
     </row>
     <row r="66">
@@ -5691,61 +5691,61 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2512712524681031</v>
+        <v>0.2456395141532432</v>
       </c>
       <c r="L66" t="n">
-        <v>0.305138893301786</v>
+        <v>0.3380092905320426</v>
       </c>
       <c r="M66" t="n">
-        <v>3.955403547984412</v>
+        <v>3.965660158081453</v>
       </c>
       <c r="N66" t="n">
-        <v>4.235928579443084</v>
+        <v>4.248262009666272</v>
       </c>
       <c r="O66" t="n">
-        <v>0.005404931039144761</v>
+        <v>0.005969627301101941</v>
       </c>
       <c r="P66" t="n">
-        <v>0.00447366921531678</v>
+        <v>0.004565080642330381</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.003736703432618531</v>
+        <v>0.003478609825007579</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01634848504939357</v>
+        <v>0.015928426234838</v>
       </c>
       <c r="S66" t="n">
-        <v>0.03054500155390393</v>
+        <v>0.02908316766815586</v>
       </c>
       <c r="T66" t="n">
-        <v>0.007290703665196573</v>
+        <v>0.008239109287673326</v>
       </c>
       <c r="U66" t="n">
-        <v>0.007260074873435269</v>
+        <v>0.007799747936383837</v>
       </c>
       <c r="V66" t="n">
-        <v>0.006201425718075152</v>
+        <v>0.005909841096096031</v>
       </c>
       <c r="W66" t="n">
-        <v>0.02214533490952547</v>
+        <v>0.02291723754645744</v>
       </c>
       <c r="X66" t="n">
-        <v>0.1682275618688141</v>
+        <v>0.149002195290762</v>
       </c>
     </row>
     <row r="67">
@@ -5771,61 +5771,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4211240356731683</v>
+        <v>0.3803330682882993</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3997137698529541</v>
+        <v>0.4020406949830687</v>
       </c>
       <c r="M67" t="n">
-        <v>4.407889787316897</v>
+        <v>4.396081402485587</v>
       </c>
       <c r="N67" t="n">
-        <v>4.344915471796567</v>
+        <v>4.340081690395644</v>
       </c>
       <c r="O67" t="n">
-        <v>0.004182986571473168</v>
+        <v>0.00470597493627709</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01078621694386006</v>
+        <v>0.01089284479685998</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.00430956785338889</v>
+        <v>0.004340232063528248</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009340045245044741</v>
+        <v>0.009832837639233902</v>
       </c>
       <c r="S67" t="n">
-        <v>0.05333489483130417</v>
+        <v>0.05410323472967622</v>
       </c>
       <c r="T67" t="n">
-        <v>0.005675132658984882</v>
+        <v>0.006130955211817612</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01133921166057252</v>
+        <v>0.01212971166427852</v>
       </c>
       <c r="V67" t="n">
-        <v>0.009639497765579491</v>
+        <v>0.009864172910482291</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0130696505554789</v>
+        <v>0.01475544444374965</v>
       </c>
       <c r="X67" t="n">
-        <v>0.07959727253584052</v>
+        <v>0.08605202936124631</v>
       </c>
     </row>
     <row r="68">
@@ -5851,61 +5851,61 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4316687937084649</v>
+        <v>0.3898978456369452</v>
       </c>
       <c r="L68" t="n">
-        <v>0.41649734086178</v>
+        <v>0.4270616471564336</v>
       </c>
       <c r="M68" t="n">
-        <v>4.511522348131344</v>
+        <v>4.499873541330101</v>
       </c>
       <c r="N68" t="n">
-        <v>4.351448479696841</v>
+        <v>4.347553934066302</v>
       </c>
       <c r="O68" t="n">
-        <v>0.00424138894137788</v>
+        <v>0.004756247585380413</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01293400812612018</v>
+        <v>0.01303020923466366</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.005306252108714812</v>
+        <v>0.005216868187635153</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01417652653712615</v>
+        <v>0.01487230500291858</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01674155348745422</v>
+        <v>0.01695949343563309</v>
       </c>
       <c r="T68" t="n">
-        <v>0.006671833150905393</v>
+        <v>0.007269573840837172</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01251769926347516</v>
+        <v>0.01304481678556396</v>
       </c>
       <c r="V68" t="n">
-        <v>0.009177833583778751</v>
+        <v>0.009115431926335764</v>
       </c>
       <c r="W68" t="n">
-        <v>0.02008302323699946</v>
+        <v>0.0224607121293263</v>
       </c>
       <c r="X68" t="n">
-        <v>0.02579373413077969</v>
+        <v>0.02689816682237356</v>
       </c>
     </row>
     <row r="69">
@@ -5931,61 +5931,61 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1562554941398336</v>
+        <v>0.1000285343957928</v>
       </c>
       <c r="L69" t="n">
-        <v>0.1860927984975772</v>
+        <v>0.1376000214334877</v>
       </c>
       <c r="M69" t="n">
-        <v>4.301187016990272</v>
+        <v>4.290484453614669</v>
       </c>
       <c r="N69" t="n">
-        <v>4.30472981637424</v>
+        <v>4.295072858247461</v>
       </c>
       <c r="O69" t="n">
-        <v>0.003147097540272044</v>
+        <v>0.003000854791929909</v>
       </c>
       <c r="P69" t="n">
-        <v>0.001787254331327555</v>
+        <v>0.001346483925043478</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.003355989857698644</v>
+        <v>0.003286974794902867</v>
       </c>
       <c r="R69" t="n">
-        <v>0.004151462438695826</v>
+        <v>0.003729024982253798</v>
       </c>
       <c r="S69" t="n">
-        <v>0.004066177963885829</v>
+        <v>0.003821443496813115</v>
       </c>
       <c r="T69" t="n">
-        <v>0.004658453729440157</v>
+        <v>0.00455663186683214</v>
       </c>
       <c r="U69" t="n">
-        <v>0.00382052070407284</v>
+        <v>0.003480099302038897</v>
       </c>
       <c r="V69" t="n">
-        <v>0.005374830332393775</v>
+        <v>0.005260231433774976</v>
       </c>
       <c r="W69" t="n">
-        <v>0.005764728644690899</v>
+        <v>0.005413433092642136</v>
       </c>
       <c r="X69" t="n">
-        <v>0.005969957525782609</v>
+        <v>0.005747973998744538</v>
       </c>
     </row>
     <row r="70">
@@ -6011,61 +6011,61 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1527928836483235</v>
+        <v>0.09682343377553043</v>
       </c>
       <c r="L70" t="n">
-        <v>0.2675350130412292</v>
+        <v>0.2153981185090495</v>
       </c>
       <c r="M70" t="n">
-        <v>4.339893559122465</v>
+        <v>4.334140788598515</v>
       </c>
       <c r="N70" t="n">
-        <v>4.373251304488082</v>
+        <v>4.365335808887848</v>
       </c>
       <c r="O70" t="n">
-        <v>0.003165967423396112</v>
+        <v>0.002981635823612692</v>
       </c>
       <c r="P70" t="n">
-        <v>0.004372072966960185</v>
+        <v>0.003850443757139979</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.005283893054565157</v>
+        <v>0.005119300208277374</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004428065283830173</v>
+        <v>0.003961724875650768</v>
       </c>
       <c r="S70" t="n">
-        <v>0.006206679560439163</v>
+        <v>0.005677537951407735</v>
       </c>
       <c r="T70" t="n">
-        <v>0.004753275643539136</v>
+        <v>0.004592007203264247</v>
       </c>
       <c r="U70" t="n">
-        <v>0.00619426940811917</v>
+        <v>0.005708048298495366</v>
       </c>
       <c r="V70" t="n">
-        <v>0.008463398056181534</v>
+        <v>0.008127003950181459</v>
       </c>
       <c r="W70" t="n">
-        <v>0.00631830776301017</v>
+        <v>0.005875808570249327</v>
       </c>
       <c r="X70" t="n">
-        <v>0.009200714701752901</v>
+        <v>0.008562651143368415</v>
       </c>
     </row>
     <row r="71">
@@ -6091,61 +6091,61 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3251980729523765</v>
+        <v>0.2678404883365064</v>
       </c>
       <c r="L71" t="n">
-        <v>0.3388589876391399</v>
+        <v>0.3051587634990652</v>
       </c>
       <c r="M71" t="n">
-        <v>4.4265321563301</v>
+        <v>4.421523566309154</v>
       </c>
       <c r="N71" t="n">
-        <v>4.442666397514478</v>
+        <v>4.440388733304707</v>
       </c>
       <c r="O71" t="n">
-        <v>0.005277935297569794</v>
+        <v>0.005065558036480573</v>
       </c>
       <c r="P71" t="n">
-        <v>0.005565805100206977</v>
+        <v>0.004884855766831945</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.004441519107726513</v>
+        <v>0.004275641635832553</v>
       </c>
       <c r="R71" t="n">
-        <v>0.005146268087504469</v>
+        <v>0.004741783479295108</v>
       </c>
       <c r="S71" t="n">
-        <v>0.005461030654635993</v>
+        <v>0.004989349104461792</v>
       </c>
       <c r="T71" t="n">
-        <v>0.007132163714276796</v>
+        <v>0.006951811543738206</v>
       </c>
       <c r="U71" t="n">
-        <v>0.006783785402912829</v>
+        <v>0.006458311425929288</v>
       </c>
       <c r="V71" t="n">
-        <v>0.007071806517176626</v>
+        <v>0.006873950893965383</v>
       </c>
       <c r="W71" t="n">
-        <v>0.006751666224067892</v>
+        <v>0.006495181441447646</v>
       </c>
       <c r="X71" t="n">
-        <v>0.006713147737019296</v>
+        <v>0.006409392042060496</v>
       </c>
     </row>
     <row r="72">
@@ -6171,61 +6171,61 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3226988012903637</v>
+        <v>0.2638017802804687</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4018753830295776</v>
+        <v>0.364729337507692</v>
       </c>
       <c r="M72" t="n">
-        <v>4.500658295365612</v>
+        <v>4.502235920367876</v>
       </c>
       <c r="N72" t="n">
-        <v>4.513339304972173</v>
+        <v>4.516127637642509</v>
       </c>
       <c r="O72" t="n">
-        <v>0.004231058406856252</v>
+        <v>0.003969755522468583</v>
       </c>
       <c r="P72" t="n">
-        <v>0.004785879916527147</v>
+        <v>0.00422008676448486</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.005253704867672498</v>
+        <v>0.00495204330355547</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004367304499079646</v>
+        <v>0.004049915939384633</v>
       </c>
       <c r="S72" t="n">
-        <v>0.005890369754721588</v>
+        <v>0.005418125503918425</v>
       </c>
       <c r="T72" t="n">
-        <v>0.005824758281389274</v>
+        <v>0.005612187405771381</v>
       </c>
       <c r="U72" t="n">
-        <v>0.006074366549045653</v>
+        <v>0.005849065215089401</v>
       </c>
       <c r="V72" t="n">
-        <v>0.008329419341902284</v>
+        <v>0.007913218039512695</v>
       </c>
       <c r="W72" t="n">
-        <v>0.006106363786393072</v>
+        <v>0.005815827053809632</v>
       </c>
       <c r="X72" t="n">
-        <v>0.007480121202695747</v>
+        <v>0.007148831460690586</v>
       </c>
     </row>
     <row r="73">
@@ -6251,61 +6251,61 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.08013831924157824</v>
+        <v>0.04031370470886774</v>
       </c>
       <c r="L73" t="n">
-        <v>0.08702574501572126</v>
+        <v>0.05057463727087248</v>
       </c>
       <c r="M73" t="n">
-        <v>4.345718815687934</v>
+        <v>4.339334217678624</v>
       </c>
       <c r="N73" t="n">
-        <v>4.333874464361721</v>
+        <v>4.329509570304954</v>
       </c>
       <c r="O73" t="n">
-        <v>0.001888412387306788</v>
+        <v>0.001836585192314117</v>
       </c>
       <c r="P73" t="n">
-        <v>0.001903126853500366</v>
+        <v>0.001545488128958874</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.00195296573515502</v>
+        <v>0.001936053547121294</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002562615128020493</v>
+        <v>0.002281901664524221</v>
       </c>
       <c r="S73" t="n">
-        <v>0.0003918587697836979</v>
+        <v>0.0002467729905005936</v>
       </c>
       <c r="T73" t="n">
-        <v>0.003426901248061201</v>
+        <v>0.003405342874213335</v>
       </c>
       <c r="U73" t="n">
-        <v>0.003470077266613913</v>
+        <v>0.003173086012973959</v>
       </c>
       <c r="V73" t="n">
-        <v>0.00361237224862</v>
+        <v>0.003581983080541543</v>
       </c>
       <c r="W73" t="n">
-        <v>0.004173805820527341</v>
+        <v>0.00396371017291886</v>
       </c>
       <c r="X73" t="n">
-        <v>0.00323384608921796</v>
+        <v>0.003149432981276837</v>
       </c>
     </row>
     <row r="74">
@@ -6331,61 +6331,61 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.08375853066839459</v>
+        <v>0.04276213165574472</v>
       </c>
       <c r="L74" t="n">
-        <v>0.1528526074727222</v>
+        <v>0.1025681890668143</v>
       </c>
       <c r="M74" t="n">
-        <v>4.36397608937349</v>
+        <v>4.360056444564394</v>
       </c>
       <c r="N74" t="n">
-        <v>4.403552325235742</v>
+        <v>4.399201030373263</v>
       </c>
       <c r="O74" t="n">
-        <v>0.001606312086320778</v>
+        <v>0.001497351395801339</v>
       </c>
       <c r="P74" t="n">
-        <v>0.002184713787554933</v>
+        <v>0.001776249493755885</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.003201077289766507</v>
+        <v>0.003159015516955978</v>
       </c>
       <c r="R74" t="n">
-        <v>0.002085950472454285</v>
+        <v>0.001906168912111457</v>
       </c>
       <c r="S74" t="n">
-        <v>0.003661090827597367</v>
+        <v>0.003449722675139116</v>
       </c>
       <c r="T74" t="n">
-        <v>0.00334045434321676</v>
+        <v>0.003265495696220424</v>
       </c>
       <c r="U74" t="n">
-        <v>0.003888931906313519</v>
+        <v>0.003488259989089588</v>
       </c>
       <c r="V74" t="n">
-        <v>0.005110530719851648</v>
+        <v>0.005034623689590515</v>
       </c>
       <c r="W74" t="n">
-        <v>0.003644334489883528</v>
+        <v>0.003493287706347263</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005529292580106506</v>
+        <v>0.005338426031883264</v>
       </c>
     </row>
     <row r="75">
@@ -6411,61 +6411,61 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2067664206129807</v>
+        <v>0.1476874036969633</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2624464874838576</v>
+        <v>0.2169097766187445</v>
       </c>
       <c r="M75" t="n">
-        <v>4.184661703848845</v>
+        <v>4.171047640784607</v>
       </c>
       <c r="N75" t="n">
-        <v>4.2908519767349</v>
+        <v>4.278071179177773</v>
       </c>
       <c r="O75" t="n">
-        <v>0.002886235977613058</v>
+        <v>0.002750447192406759</v>
       </c>
       <c r="P75" t="n">
-        <v>0.004487339328524661</v>
+        <v>0.003952612232653929</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.004028529442128123</v>
+        <v>0.003921053776456239</v>
       </c>
       <c r="R75" t="n">
-        <v>0.00473031133853227</v>
+        <v>0.004291608435658732</v>
       </c>
       <c r="S75" t="n">
-        <v>0.007146110922988586</v>
+        <v>0.006818495129827107</v>
       </c>
       <c r="T75" t="n">
-        <v>0.004392805883387863</v>
+        <v>0.004283318148060207</v>
       </c>
       <c r="U75" t="n">
-        <v>0.005968410581595977</v>
+        <v>0.005536910583288933</v>
       </c>
       <c r="V75" t="n">
-        <v>0.006396828988319664</v>
+        <v>0.006228825851268639</v>
       </c>
       <c r="W75" t="n">
-        <v>0.006426465169334155</v>
+        <v>0.00608260747422677</v>
       </c>
       <c r="X75" t="n">
-        <v>0.01080740736083336</v>
+        <v>0.01043509687905746</v>
       </c>
     </row>
     <row r="76">
@@ -6491,61 +6491,61 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02041481449548191</v>
+        <v>0.006316940755609539</v>
       </c>
       <c r="L76" t="n">
-        <v>0.02255561574794553</v>
+        <v>0.008479839422888345</v>
       </c>
       <c r="M76" t="n">
-        <v>4.335730785167194</v>
+        <v>4.333353832661424</v>
       </c>
       <c r="N76" t="n">
-        <v>4.319303662095504</v>
+        <v>4.317490078028524</v>
       </c>
       <c r="O76" t="n">
-        <v>0.00193138604073707</v>
+        <v>0.0019048094539966</v>
       </c>
       <c r="P76" t="n">
-        <v>0.001206419819451297</v>
+        <v>0.001105329039509073</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.001943079122286904</v>
+        <v>0.001942535760760942</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002220330720090912</v>
+        <v>0.002111653341818055</v>
       </c>
       <c r="S76" t="n">
-        <v>0.0007935819215516187</v>
+        <v>0.0007572342869350446</v>
       </c>
       <c r="T76" t="n">
-        <v>0.003560047100253156</v>
+        <v>0.003555241699748322</v>
       </c>
       <c r="U76" t="n">
-        <v>0.002858746704015702</v>
+        <v>0.002807197363610444</v>
       </c>
       <c r="V76" t="n">
-        <v>0.00358430663273694</v>
+        <v>0.003576309549742578</v>
       </c>
       <c r="W76" t="n">
-        <v>0.003747183649823626</v>
+        <v>0.003689721161253848</v>
       </c>
       <c r="X76" t="n">
-        <v>0.002698712607651203</v>
+        <v>0.002685457593809299</v>
       </c>
     </row>
     <row r="77">
@@ -6571,61 +6571,61 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0375161600995857</v>
+        <v>0.01454057165154276</v>
       </c>
       <c r="L77" t="n">
-        <v>0.09091298140267795</v>
+        <v>0.05104071392674532</v>
       </c>
       <c r="M77" t="n">
-        <v>4.235925950677315</v>
+        <v>4.230706129780605</v>
       </c>
       <c r="N77" t="n">
-        <v>4.251760422935557</v>
+        <v>4.241902354927587</v>
       </c>
       <c r="O77" t="n">
-        <v>0.001790754486881807</v>
+        <v>0.001728579813357431</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0005576038270875812</v>
+        <v>0.0003318260811728798</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.0022377454173005</v>
+        <v>0.002216589733130873</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0003472352486419925</v>
+        <v>0.0002815277239335915</v>
       </c>
       <c r="S77" t="n">
-        <v>0.001774568129447606</v>
+        <v>0.001675355746545451</v>
       </c>
       <c r="T77" t="n">
-        <v>0.002810193921065609</v>
+        <v>0.002776187633144704</v>
       </c>
       <c r="U77" t="n">
-        <v>0.001984966423812922</v>
+        <v>0.001776660370824875</v>
       </c>
       <c r="V77" t="n">
-        <v>0.003305775828502809</v>
+        <v>0.003273020895314783</v>
       </c>
       <c r="W77" t="n">
-        <v>0.002013132349266835</v>
+        <v>0.001962948714231</v>
       </c>
       <c r="X77" t="n">
-        <v>0.002768444124214075</v>
+        <v>0.002704279506017001</v>
       </c>
     </row>
     <row r="78">
@@ -6651,61 +6651,61 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02699802811307632</v>
+        <v>0.009175722573668135</v>
       </c>
       <c r="L78" t="n">
-        <v>0.07884453720528377</v>
+        <v>0.04320188478660273</v>
       </c>
       <c r="M78" t="n">
-        <v>4.377810298060794</v>
+        <v>4.366330804420246</v>
       </c>
       <c r="N78" t="n">
-        <v>4.386199663350345</v>
+        <v>4.369076403133636</v>
       </c>
       <c r="O78" t="n">
-        <v>0.000771433786867778</v>
+        <v>0.0007203392633440642</v>
       </c>
       <c r="P78" t="n">
-        <v>1.000000000006614e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.00186954059648756</v>
+        <v>0.001914066894694201</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0001599966328199954</v>
+        <v>0.00011006026955287</v>
       </c>
       <c r="S78" t="n">
-        <v>1.000000000001471e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="T78" t="n">
-        <v>0.002042032089348669</v>
+        <v>0.002009510143615828</v>
       </c>
       <c r="U78" t="n">
-        <v>0.002340233760396255</v>
+        <v>0.002280258950356349</v>
       </c>
       <c r="V78" t="n">
-        <v>0.00295903386307918</v>
+        <v>0.003004821614199075</v>
       </c>
       <c r="W78" t="n">
-        <v>0.001703448986633627</v>
+        <v>0.00166135625112434</v>
       </c>
       <c r="X78" t="n">
-        <v>0.002928232256476276</v>
+        <v>0.00302015018658533</v>
       </c>
     </row>
     <row r="79">
@@ -6725,67 +6725,67 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2887378674060793</v>
+        <v>0.2286775418539777</v>
       </c>
       <c r="L79" t="n">
-        <v>0.28961502997839</v>
+        <v>0.2476984005019057</v>
       </c>
       <c r="M79" t="n">
-        <v>4.358789254115512</v>
+        <v>4.343239893866217</v>
       </c>
       <c r="N79" t="n">
-        <v>4.385205411533307</v>
+        <v>4.418846948554335</v>
       </c>
       <c r="O79" t="n">
-        <v>0.001792394564382161</v>
+        <v>0.001716670584802468</v>
       </c>
       <c r="P79" t="n">
-        <v>0.0009492857379808609</v>
+        <v>0.0007701143652709886</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.001301995940293981</v>
+        <v>0.001254266560138549</v>
       </c>
       <c r="R79" t="n">
-        <v>0.001564506408444912</v>
+        <v>0.001377094527512765</v>
       </c>
       <c r="S79" t="n">
-        <v>0.009529623992513012</v>
+        <v>1.000000000000728e-05</v>
       </c>
       <c r="T79" t="n">
-        <v>0.003035577471188402</v>
+        <v>0.002486272629361943</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002106800586566564</v>
+        <v>0.00178425523747522</v>
       </c>
       <c r="V79" t="n">
-        <v>0.002389004431315216</v>
+        <v>0.002214018072321555</v>
       </c>
       <c r="W79" t="n">
-        <v>0.002821008819136486</v>
+        <v>0.002289673483783877</v>
       </c>
       <c r="X79" t="n">
-        <v>5.015224827991929</v>
+        <v>0.1469243680567952</v>
       </c>
     </row>
     <row r="80">
@@ -6805,67 +6805,67 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1595546616330362</v>
+        <v>0.1016449187314903</v>
       </c>
       <c r="L80" t="n">
-        <v>0.1839706279446391</v>
+        <v>0.1455773989161053</v>
       </c>
       <c r="M80" t="n">
-        <v>4.445589425954382</v>
+        <v>4.435466917526268</v>
       </c>
       <c r="N80" t="n">
-        <v>4.445854305647299</v>
+        <v>4.443449495714573</v>
       </c>
       <c r="O80" t="n">
-        <v>0.001741262448409344</v>
+        <v>0.001654506639507853</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0009025119194282157</v>
+        <v>0.0007555556669410075</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.001485143299012809</v>
+        <v>0.00146559569458513</v>
       </c>
       <c r="R80" t="n">
-        <v>0.001607557060719054</v>
+        <v>0.001451087086994119</v>
       </c>
       <c r="S80" t="n">
-        <v>0.01484200360652649</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T80" t="n">
-        <v>0.003004235179839869</v>
+        <v>0.002537006128574125</v>
       </c>
       <c r="U80" t="n">
-        <v>0.00217814447531208</v>
+        <v>0.001540133415001079</v>
       </c>
       <c r="V80" t="n">
-        <v>0.002696731783359017</v>
+        <v>0.002494368951688649</v>
       </c>
       <c r="W80" t="n">
-        <v>0.003030596545972111</v>
+        <v>0.002253417760032409</v>
       </c>
       <c r="X80" t="n">
-        <v>18.85349337514079</v>
+        <v>19832.28835652163</v>
       </c>
     </row>
     <row r="81">
@@ -6885,67 +6885,67 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2672160292479843</v>
+        <v>0.218460323060076</v>
       </c>
       <c r="L81" t="n">
-        <v>0.2463010363382412</v>
+        <v>0.2074917963802061</v>
       </c>
       <c r="M81" t="n">
-        <v>4.565126561556436</v>
+        <v>4.558610219689992</v>
       </c>
       <c r="N81" t="n">
-        <v>4.554982416853693</v>
+        <v>4.542924221823536</v>
       </c>
       <c r="O81" t="n">
-        <v>0.001753475480766125</v>
+        <v>0.00168220394356639</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0009922329881059064</v>
+        <v>0.0008133511555461013</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.001089174560856491</v>
+        <v>0.001049978943833308</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001625173111145305</v>
+        <v>0.001510233064846092</v>
       </c>
       <c r="S81" t="n">
-        <v>0.001087619558056312</v>
+        <v>0.4999999999902024</v>
       </c>
       <c r="T81" t="n">
-        <v>0.002811230821345343</v>
+        <v>0.002584971826882645</v>
       </c>
       <c r="U81" t="n">
-        <v>0.001951648662707762</v>
+        <v>0.00171074543356312</v>
       </c>
       <c r="V81" t="n">
-        <v>0.001975739555301541</v>
+        <v>0.0018659248282199</v>
       </c>
       <c r="W81" t="n">
-        <v>0.002541709110667261</v>
+        <v>0.002217472387008815</v>
       </c>
       <c r="X81" t="n">
-        <v>0.2444911013592787</v>
+        <v>18848.5743473663</v>
       </c>
     </row>
     <row r="82">
@@ -6965,67 +6965,67 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1476585777734352</v>
+        <v>0.1388222346861923</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1784005676162389</v>
+        <v>0.1494984216229154</v>
       </c>
       <c r="M82" t="n">
-        <v>4.56381144856591</v>
+        <v>4.55959061557802</v>
       </c>
       <c r="N82" t="n">
-        <v>4.581482154898716</v>
+        <v>4.561643240662769</v>
       </c>
       <c r="O82" t="n">
-        <v>0.001930780953949052</v>
+        <v>0.001877750805989576</v>
       </c>
       <c r="P82" t="n">
-        <v>0.0008453818148484649</v>
+        <v>0.0007655602694265002</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.001121038279680322</v>
+        <v>0.001082780357006867</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001732956824903161</v>
+        <v>0.001654354304383516</v>
       </c>
       <c r="S82" t="n">
-        <v>1e-05</v>
+        <v>0.001052414506449224</v>
       </c>
       <c r="T82" t="n">
-        <v>0.00318380785313367</v>
+        <v>0.002966774631178096</v>
       </c>
       <c r="U82" t="n">
-        <v>0.00230973866986764</v>
+        <v>0.002897145466427231</v>
       </c>
       <c r="V82" t="n">
-        <v>0.002111991859561404</v>
+        <v>0.001965793635841357</v>
       </c>
       <c r="W82" t="n">
-        <v>0.002699433726972718</v>
+        <v>0.002572427706274657</v>
       </c>
       <c r="X82" t="n">
-        <v>0.1649916789094458</v>
+        <v>0.4818004532944868</v>
       </c>
     </row>
     <row r="83">
@@ -7045,65 +7045,65 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1893204027356125</v>
+        <v>0.1276873733991883</v>
       </c>
       <c r="L83" t="n">
-        <v>0.1633880598032415</v>
+        <v>0.1238780907614875</v>
       </c>
       <c r="M83" t="n">
-        <v>4.564646219566645</v>
+        <v>4.58025111211242</v>
       </c>
       <c r="N83" t="n">
-        <v>4.536129375014693</v>
+        <v>4.567815266695854</v>
       </c>
       <c r="O83" t="n">
-        <v>0.001344665533120288</v>
+        <v>0.001287215248476235</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0005232410122737074</v>
+        <v>0.0004138832761044285</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.0009109933047170348</v>
+        <v>0.0008968433687017304</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001426911882632896</v>
+        <v>0.001320150392884276</v>
       </c>
       <c r="S83" t="n">
-        <v>0.003414359058118181</v>
+        <v>1.000000000000291e-05</v>
       </c>
       <c r="T83" t="n">
-        <v>0.002298294605313423</v>
+        <v>0.002045797918348906</v>
       </c>
       <c r="U83" t="n">
-        <v>0.001851668291098452</v>
+        <v>0.001499398790370192</v>
       </c>
       <c r="V83" t="n">
-        <v>0.0017648148443495</v>
+        <v>0.001676726426882854</v>
       </c>
       <c r="W83" t="n">
-        <v>0.002535342078807969</v>
+        <v>0.002088774871117691</v>
       </c>
       <c r="X83" t="n">
-        <v>1.272899481411111</v>
+        <v>0.1848734143346477</v>
       </c>
     </row>
     <row r="84">
@@ -7123,65 +7123,65 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.168261400395764</v>
+        <v>0.08086517134350701</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2390632443581008</v>
+        <v>0.2380875694974745</v>
       </c>
       <c r="M84" t="n">
-        <v>4.508063070964528</v>
+        <v>3.412699872579033</v>
       </c>
       <c r="N84" t="n">
-        <v>4.520761213309592</v>
+        <v>4.470754799896725</v>
       </c>
       <c r="O84" t="n">
-        <v>0.001657357108984876</v>
+        <v>0.001522950716886235</v>
       </c>
       <c r="P84" t="n">
-        <v>1.000000000000002e-05</v>
+        <v>1e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.00171372491068584</v>
+        <v>0.002077821589071728</v>
       </c>
       <c r="R84" t="n">
-        <v>0.001993279007063037</v>
+        <v>0.001889143763259511</v>
       </c>
       <c r="S84" t="n">
-        <v>1e-05</v>
+        <v>0.4999987012522787</v>
       </c>
       <c r="T84" t="n">
-        <v>0.00261843187953057</v>
+        <v>0.002253411022098677</v>
       </c>
       <c r="U84" t="n">
-        <v>0.002574073651979341</v>
+        <v>0.003925119669622386</v>
       </c>
       <c r="V84" t="n">
-        <v>0.003104856553156294</v>
+        <v>0.005253354567083451</v>
       </c>
       <c r="W84" t="n">
-        <v>0.003208496211025895</v>
+        <v>0.003954512995103103</v>
       </c>
       <c r="X84" t="n">
-        <v>0.1142609563625063</v>
+        <v>6548.710159818389</v>
       </c>
     </row>
     <row r="85">
@@ -7201,65 +7201,67 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.232384799749474</v>
+        <v>0.2341581070084072</v>
       </c>
       <c r="L85" t="n">
-        <v>0.2781512948803044</v>
+        <v>0.2184863971810316</v>
       </c>
       <c r="M85" t="n">
-        <v>4.4579287131415</v>
+        <v>4.338754752871145</v>
       </c>
       <c r="N85" t="n">
-        <v>4.497049257515203</v>
+        <v>4.379413036095525</v>
       </c>
       <c r="O85" t="n">
-        <v>0.001537875382336928</v>
+        <v>0.001745242921752755</v>
       </c>
       <c r="P85" t="n">
-        <v>1e-05</v>
+        <v>0.0007291841706355109</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.001458136366543977</v>
+        <v>0.001021266876925764</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001725956047497303</v>
+        <v>0.001373785965154264</v>
       </c>
       <c r="S85" t="n">
-        <v>1e-05</v>
+        <v>0.4999999999999009</v>
       </c>
       <c r="T85" t="n">
-        <v>0.002395020191171236</v>
+        <v>0.00271496998866605</v>
       </c>
       <c r="U85" t="n">
-        <v>0.004200673022294778</v>
+        <v>0.001701257733882546</v>
       </c>
       <c r="V85" t="n">
-        <v>0.002753015890121723</v>
+        <v>0.001843236389347277</v>
       </c>
       <c r="W85" t="n">
-        <v>0.002670816987996213</v>
+        <v>0.002037874868636181</v>
       </c>
       <c r="X85" t="n">
-        <v>0.1232236662676461</v>
+        <v>20271.73251492424</v>
       </c>
     </row>
     <row r="86">
@@ -7279,65 +7281,67 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1217276426814131</v>
+        <v>0.1048616667183305</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5514474416442302</v>
+        <v>0.1405580162930134</v>
       </c>
       <c r="M86" t="n">
-        <v>4.465527496290664</v>
+        <v>4.45685408733002</v>
       </c>
       <c r="N86" t="n">
-        <v>4.582344917039739</v>
+        <v>4.450371634163849</v>
       </c>
       <c r="O86" t="n">
-        <v>0.002099607246554858</v>
+        <v>0.001580791614561185</v>
       </c>
       <c r="P86" t="n">
-        <v>0.00184594255573129</v>
+        <v>0.0007120201989102038</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.01589558721728189</v>
+        <v>0.001384678082003281</v>
       </c>
       <c r="R86" t="n">
-        <v>0.003735621257268642</v>
+        <v>0.001509620312503968</v>
       </c>
       <c r="S86" t="n">
-        <v>1.000002279131508e-05</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="T86" t="n">
-        <v>0.003276875876862828</v>
+        <v>0.002421173880689751</v>
       </c>
       <c r="U86" t="n">
-        <v>0.00481359642362809</v>
+        <v>0.001889342138122303</v>
       </c>
       <c r="V86" t="n">
-        <v>0.3020998465308165</v>
+        <v>0.002380775142018067</v>
       </c>
       <c r="W86" t="n">
-        <v>0.005901742687745915</v>
+        <v>0.00235963091482602</v>
       </c>
       <c r="X86" t="n">
-        <v>0.03620911370556244</v>
+        <v>30397.65605925169</v>
       </c>
     </row>
     <row r="87">
@@ -7357,65 +7361,67 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1836792919038959</v>
+        <v>0.1625122195698727</v>
       </c>
       <c r="L87" t="n">
-        <v>0.2895806109828785</v>
+        <v>0.1593672433302182</v>
       </c>
       <c r="M87" t="n">
-        <v>4.626284423183901</v>
+        <v>4.559708044000981</v>
       </c>
       <c r="N87" t="n">
-        <v>4.64001678621832</v>
+        <v>4.552096859177026</v>
       </c>
       <c r="O87" t="n">
-        <v>0.001943392102663628</v>
+        <v>0.00200473783582211</v>
       </c>
       <c r="P87" t="n">
-        <v>1.000000000000005e-05</v>
+        <v>0.0009903107674953146</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.002136665946868873</v>
+        <v>0.001294573787692988</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002211463667730281</v>
+        <v>0.001814746237459998</v>
       </c>
       <c r="S87" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>0.001564399876615501</v>
       </c>
       <c r="T87" t="n">
-        <v>0.00315205020070995</v>
+        <v>0.003230164113287518</v>
       </c>
       <c r="U87" t="n">
-        <v>0.004666913087165572</v>
+        <v>0.002734512251127585</v>
       </c>
       <c r="V87" t="n">
-        <v>0.004128715143231171</v>
+        <v>0.002328571613085184</v>
       </c>
       <c r="W87" t="n">
-        <v>0.00351839916875652</v>
+        <v>0.002793482181689642</v>
       </c>
       <c r="X87" t="n">
-        <v>0.1147227087051909</v>
+        <v>0.5931109352819993</v>
       </c>
     </row>
     <row r="88">
@@ -7435,65 +7441,67 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2310798297965026</v>
+        <v>0.2203248872293976</v>
       </c>
       <c r="L88" t="n">
-        <v>0.1753064279150189</v>
+        <v>0.2156387291342206</v>
       </c>
       <c r="M88" t="n">
-        <v>4.585737126599059</v>
+        <v>4.564397093213429</v>
       </c>
       <c r="N88" t="n">
-        <v>4.622456855907859</v>
+        <v>4.543714605127302</v>
       </c>
       <c r="O88" t="n">
-        <v>0.001608730948906043</v>
+        <v>0.001810751539512169</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0001796904817266535</v>
+        <v>0.0009679949847219105</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0008582863551974858</v>
+        <v>0.001140473998437496</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001384085571603225</v>
+        <v>0.001661065765831293</v>
       </c>
       <c r="S88" t="n">
-        <v>1.000000000000001e-05</v>
+        <v>0.496457408050297</v>
       </c>
       <c r="T88" t="n">
-        <v>0.002573233978364011</v>
+        <v>0.00318254833125473</v>
       </c>
       <c r="U88" t="n">
-        <v>0.003582094524999696</v>
+        <v>0.002964496658130539</v>
       </c>
       <c r="V88" t="n">
-        <v>0.001605927406442038</v>
+        <v>0.002167720709674138</v>
       </c>
       <c r="W88" t="n">
-        <v>0.002164241149141322</v>
+        <v>0.003125957041430961</v>
       </c>
       <c r="X88" t="n">
-        <v>0.1745611462131772</v>
+        <v>20360.51335535758</v>
       </c>
     </row>
     <row r="89">
@@ -7513,65 +7521,65 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3391853656933783</v>
+        <v>0.2930745491696932</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3168259626150547</v>
+        <v>0.2724676411712534</v>
       </c>
       <c r="M89" t="n">
-        <v>4.50704372858565</v>
+        <v>4.501956059923095</v>
       </c>
       <c r="N89" t="n">
-        <v>4.604934684634735</v>
+        <v>4.555634741953829</v>
       </c>
       <c r="O89" t="n">
-        <v>0.00247825280917152</v>
+        <v>0.002329407921218432</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0007928172237319195</v>
+        <v>0.0004171190078032905</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.001390789113991187</v>
+        <v>0.001380245350722544</v>
       </c>
       <c r="R89" t="n">
-        <v>0.001926328709113568</v>
+        <v>0.001785358529801925</v>
       </c>
       <c r="S89" t="n">
-        <v>1.000000000013837e-05</v>
+        <v>0.4999999999999986</v>
       </c>
       <c r="T89" t="n">
-        <v>0.004068897943510819</v>
+        <v>0.00375834783629152</v>
       </c>
       <c r="U89" t="n">
-        <v>0.003234652637752004</v>
+        <v>0.00327729720402463</v>
       </c>
       <c r="V89" t="n">
-        <v>0.002427627796831223</v>
+        <v>0.002432842663059057</v>
       </c>
       <c r="W89" t="n">
-        <v>0.002849371281648917</v>
+        <v>0.002596398401004339</v>
       </c>
       <c r="X89" t="n">
-        <v>0.07245185294382121</v>
+        <v>12534.68808562292</v>
       </c>
     </row>
     <row r="90">
@@ -7593,63 +7601,65 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.226725035550164</v>
+        <v>0.4648934235510216</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4822804007927045</v>
+        <v>0.5375862892717396</v>
       </c>
       <c r="M90" t="n">
-        <v>4.483427880631227</v>
+        <v>4.563095274616819</v>
       </c>
       <c r="N90" t="n">
-        <v>4.281175338829785</v>
+        <v>4.297797203619493</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003646640808512429</v>
+        <v>0.003722050759834601</v>
       </c>
       <c r="P90" t="n">
-        <v>0.00351970081889255</v>
+        <v>0.004598593363508691</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.006395037972092299</v>
+        <v>0.007069349618031633</v>
       </c>
       <c r="R90" t="n">
-        <v>0.009864437979951209</v>
+        <v>0.01166290266716484</v>
       </c>
       <c r="S90" t="n">
-        <v>0.002845805225587108</v>
+        <v>0.002137468097633341</v>
       </c>
       <c r="T90" t="n">
-        <v>0.006888857177997446</v>
+        <v>0.006219046418025961</v>
       </c>
       <c r="U90" t="n">
-        <v>0.005845857911156931</v>
+        <v>0.006253792358382476</v>
       </c>
       <c r="V90" t="n">
-        <v>0.01239214452302125</v>
+        <v>0.006726856055988481</v>
       </c>
       <c r="W90" t="n">
-        <v>0.02567462680068399</v>
+        <v>0.02700978036802896</v>
       </c>
       <c r="X90" t="n">
-        <v>0.1140836611531454</v>
+        <v>0.06029913645068642</v>
       </c>
     </row>
   </sheetData>
